--- a/research/traditional_assets/database/data/russia/russia_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/russia/russia_metals_mining.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1279570182899178</v>
+        <v>0.127737104253338</v>
       </c>
       <c r="C2">
-        <v>14413.95005280922</v>
+        <v>14309.90297187257</v>
       </c>
       <c r="D2">
-        <v>13088.95005280922</v>
+        <v>13124.07997187257</v>
       </c>
       <c r="E2">
-        <v>-7705</v>
+        <v>-7565.823</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>139.177</v>
       </c>
       <c r="G2">
         <v>1325</v>
@@ -1445,28 +1445,28 @@
         <v>1577.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>7.000603100000001</v>
       </c>
       <c r="N2">
-        <v>1577.5</v>
+        <v>1570.4993969</v>
       </c>
       <c r="O2">
-        <v>315.5</v>
+        <v>314.09987938</v>
       </c>
       <c r="P2">
-        <v>1262</v>
+        <v>1256.39951752</v>
       </c>
       <c r="Q2">
-        <v>1287</v>
+        <v>1281.39951752</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1279570182899178</v>
+        <v>0.12862091338721</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652959</v>
+        <v>0.9921732014613791</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>225.3377284022858</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.127737104253338</v>
+        <v>0.1275171902167581</v>
       </c>
       <c r="C3">
-        <v>14309.90297187257</v>
+        <v>14206.04497140444</v>
       </c>
       <c r="D3">
-        <v>13124.07997187257</v>
+        <v>13159.39897140444</v>
       </c>
       <c r="E3">
-        <v>-7565.823</v>
+        <v>-7426.646</v>
       </c>
       <c r="F3">
-        <v>139.177</v>
+        <v>278.354</v>
       </c>
       <c r="G3">
         <v>1325</v>
@@ -1527,28 +1527,28 @@
         <v>1577.5</v>
       </c>
       <c r="M3">
-        <v>7.000603100000001</v>
+        <v>14.0012062</v>
       </c>
       <c r="N3">
-        <v>1570.4993969</v>
+        <v>1563.4987938</v>
       </c>
       <c r="O3">
-        <v>314.09987938</v>
+        <v>312.69975876</v>
       </c>
       <c r="P3">
-        <v>1256.39951752</v>
+        <v>1250.79903504</v>
       </c>
       <c r="Q3">
-        <v>1281.39951752</v>
+        <v>1275.79903504</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.12862091338721</v>
+        <v>0.1292983573640389</v>
       </c>
       <c r="T3">
-        <v>0.9921732014613791</v>
+        <v>1.000288805743097</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>225.3377284022858</v>
+        <v>112.6688642011429</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1275171902167581</v>
+        <v>0.1272972761801783</v>
       </c>
       <c r="C4">
-        <v>14206.04497140444</v>
+        <v>14102.37758206146</v>
       </c>
       <c r="D4">
-        <v>13159.39897140444</v>
+        <v>13194.90858206146</v>
       </c>
       <c r="E4">
-        <v>-7426.646</v>
+        <v>-7287.469</v>
       </c>
       <c r="F4">
-        <v>278.354</v>
+        <v>417.531</v>
       </c>
       <c r="G4">
         <v>1325</v>
@@ -1609,28 +1609,28 @@
         <v>1577.5</v>
       </c>
       <c r="M4">
-        <v>14.0012062</v>
+        <v>21.0018093</v>
       </c>
       <c r="N4">
-        <v>1563.4987938</v>
+        <v>1556.4981907</v>
       </c>
       <c r="O4">
-        <v>312.69975876</v>
+        <v>311.29963814</v>
       </c>
       <c r="P4">
-        <v>1250.79903504</v>
+        <v>1245.19855256</v>
       </c>
       <c r="Q4">
-        <v>1275.79903504</v>
+        <v>1270.19855256</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1292983573640389</v>
+        <v>0.1299897692579157</v>
       </c>
       <c r="T4">
-        <v>1.000288805743097</v>
+        <v>1.00857174207186</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>112.6688642011429</v>
+        <v>75.11257613409526</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1272972761801783</v>
+        <v>0.1270773621435984</v>
       </c>
       <c r="C5">
-        <v>14102.37758206146</v>
+        <v>13998.90235106642</v>
       </c>
       <c r="D5">
-        <v>13194.90858206146</v>
+        <v>13230.61035106642</v>
       </c>
       <c r="E5">
-        <v>-7287.469</v>
+        <v>-7148.291999999999</v>
       </c>
       <c r="F5">
-        <v>417.531</v>
+        <v>556.7080000000001</v>
       </c>
       <c r="G5">
         <v>1325</v>
@@ -1691,28 +1691,28 @@
         <v>1577.5</v>
       </c>
       <c r="M5">
-        <v>21.0018093</v>
+        <v>28.0024124</v>
       </c>
       <c r="N5">
-        <v>1556.4981907</v>
+        <v>1549.4975876</v>
       </c>
       <c r="O5">
-        <v>311.29963814</v>
+        <v>309.89951752</v>
       </c>
       <c r="P5">
-        <v>1245.19855256</v>
+        <v>1239.59807008</v>
       </c>
       <c r="Q5">
-        <v>1270.19855256</v>
+        <v>1264.59807008</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1299897692579157</v>
+        <v>0.1306955855662484</v>
       </c>
       <c r="T5">
-        <v>1.00857174207186</v>
+        <v>1.017027239574139</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>75.11257613409526</v>
+        <v>56.33443210057144</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1270773621435984</v>
+        <v>0.1268574481070186</v>
       </c>
       <c r="C6">
-        <v>13998.90235106642</v>
+        <v>13895.62084243295</v>
       </c>
       <c r="D6">
-        <v>13230.61035106642</v>
+        <v>13266.50584243295</v>
       </c>
       <c r="E6">
-        <v>-7148.291999999999</v>
+        <v>-7009.115</v>
       </c>
       <c r="F6">
-        <v>556.7080000000001</v>
+        <v>695.8850000000001</v>
       </c>
       <c r="G6">
         <v>1325</v>
@@ -1773,28 +1773,28 @@
         <v>1577.5</v>
       </c>
       <c r="M6">
-        <v>28.0024124</v>
+        <v>35.0030155</v>
       </c>
       <c r="N6">
-        <v>1549.4975876</v>
+        <v>1542.4969845</v>
       </c>
       <c r="O6">
-        <v>309.89951752</v>
+        <v>308.4993969</v>
       </c>
       <c r="P6">
-        <v>1239.59807008</v>
+        <v>1233.9975876</v>
       </c>
       <c r="Q6">
-        <v>1264.59807008</v>
+        <v>1258.9975876</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1306955855662484</v>
+        <v>0.1314162611652827</v>
       </c>
       <c r="T6">
-        <v>1.017027239574139</v>
+        <v>1.02566074755015</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.33443210057144</v>
+        <v>45.06754568045716</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1268574481070186</v>
+        <v>0.1266375340704388</v>
       </c>
       <c r="C7">
-        <v>13895.62084243295</v>
+        <v>13792.53463719392</v>
       </c>
       <c r="D7">
-        <v>13266.50584243295</v>
+        <v>13302.59663719392</v>
       </c>
       <c r="E7">
-        <v>-7009.115</v>
+        <v>-6869.938</v>
       </c>
       <c r="F7">
-        <v>695.8850000000001</v>
+        <v>835.0620000000001</v>
       </c>
       <c r="G7">
         <v>1325</v>
@@ -1855,28 +1855,28 @@
         <v>1577.5</v>
       </c>
       <c r="M7">
-        <v>35.0030155</v>
+        <v>42.0036186</v>
       </c>
       <c r="N7">
-        <v>1542.4969845</v>
+        <v>1535.4963814</v>
       </c>
       <c r="O7">
-        <v>308.4993969</v>
+        <v>307.09927628</v>
       </c>
       <c r="P7">
-        <v>1233.9975876</v>
+        <v>1228.39710512</v>
       </c>
       <c r="Q7">
-        <v>1258.9975876</v>
+        <v>1253.39710512</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1314162611652827</v>
+        <v>0.1321522702877008</v>
       </c>
       <c r="T7">
-        <v>1.02566074755015</v>
+        <v>1.034477947185226</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.06754568045716</v>
+        <v>37.55628806704763</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1266375340704388</v>
+        <v>0.126417620033859</v>
       </c>
       <c r="C8">
-        <v>13792.53463719392</v>
+        <v>13689.6453336336</v>
       </c>
       <c r="D8">
-        <v>13302.59663719392</v>
+        <v>13338.8843336336</v>
       </c>
       <c r="E8">
-        <v>-6869.938</v>
+        <v>-6730.761</v>
       </c>
       <c r="F8">
-        <v>835.062</v>
+        <v>974.2389999999999</v>
       </c>
       <c r="G8">
         <v>1325</v>
@@ -1937,28 +1937,28 @@
         <v>1577.5</v>
       </c>
       <c r="M8">
-        <v>42.0036186</v>
+        <v>49.0042217</v>
       </c>
       <c r="N8">
-        <v>1535.4963814</v>
+        <v>1528.4957783</v>
       </c>
       <c r="O8">
-        <v>307.09927628</v>
+        <v>305.69915566</v>
       </c>
       <c r="P8">
-        <v>1228.39710512</v>
+        <v>1222.79662264</v>
       </c>
       <c r="Q8">
-        <v>1253.39710512</v>
+        <v>1247.79662264</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1321522702877008</v>
+        <v>0.1329041075632892</v>
       </c>
       <c r="T8">
-        <v>1.034477947185226</v>
+        <v>1.043484764016755</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.55628806704764</v>
+        <v>32.1911040574694</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1264176200338589</v>
+        <v>0.1261977059972791</v>
       </c>
       <c r="C9">
-        <v>13689.64533363361</v>
+        <v>13586.95454752359</v>
       </c>
       <c r="D9">
-        <v>13338.88433363361</v>
+        <v>13375.37054752359</v>
       </c>
       <c r="E9">
-        <v>-6730.761</v>
+        <v>-6591.584</v>
       </c>
       <c r="F9">
-        <v>974.2390000000001</v>
+        <v>1113.416</v>
       </c>
       <c r="G9">
         <v>1325</v>
@@ -2019,28 +2019,28 @@
         <v>1577.5</v>
       </c>
       <c r="M9">
-        <v>49.0042217</v>
+        <v>56.00482480000001</v>
       </c>
       <c r="N9">
-        <v>1528.4957783</v>
+        <v>1521.4951752</v>
       </c>
       <c r="O9">
-        <v>305.69915566</v>
+        <v>304.29903504</v>
       </c>
       <c r="P9">
-        <v>1222.79662264</v>
+        <v>1217.19614016</v>
       </c>
       <c r="Q9">
-        <v>1247.79662264</v>
+        <v>1242.19614016</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1329041075632892</v>
+        <v>0.1336722891274773</v>
       </c>
       <c r="T9">
-        <v>1.043484764016755</v>
+        <v>1.052687381214186</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.1911040574694</v>
+        <v>28.16721605028572</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1261977059972791</v>
+        <v>0.1259777919606993</v>
       </c>
       <c r="C10">
-        <v>13586.95454752359</v>
+        <v>13484.4639123626</v>
       </c>
       <c r="D10">
-        <v>13375.37054752359</v>
+        <v>13412.0569123626</v>
       </c>
       <c r="E10">
-        <v>-6591.584</v>
+        <v>-6452.407</v>
       </c>
       <c r="F10">
-        <v>1113.416</v>
+        <v>1252.593</v>
       </c>
       <c r="G10">
         <v>1325</v>
@@ -2101,28 +2101,28 @@
         <v>1577.5</v>
       </c>
       <c r="M10">
-        <v>56.00482480000001</v>
+        <v>63.0054279</v>
       </c>
       <c r="N10">
-        <v>1521.4951752</v>
+        <v>1514.4945721</v>
       </c>
       <c r="O10">
-        <v>304.29903504</v>
+        <v>302.89891442</v>
       </c>
       <c r="P10">
-        <v>1217.19614016</v>
+        <v>1211.59565768</v>
       </c>
       <c r="Q10">
-        <v>1242.19614016</v>
+        <v>1236.59565768</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1336722891274773</v>
+        <v>0.1344573538029662</v>
       </c>
       <c r="T10">
-        <v>1.052687381214186</v>
+        <v>1.062092253734638</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.16721605028572</v>
+        <v>25.03752537803175</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1259777919606993</v>
+        <v>0.1257578779241194</v>
       </c>
       <c r="C11">
-        <v>13484.4639123626</v>
+        <v>13382.17507962031</v>
       </c>
       <c r="D11">
-        <v>13412.0569123626</v>
+        <v>13448.94507962031</v>
       </c>
       <c r="E11">
-        <v>-6452.407</v>
+        <v>-6313.23</v>
       </c>
       <c r="F11">
-        <v>1252.593</v>
+        <v>1391.77</v>
       </c>
       <c r="G11">
         <v>1325</v>
@@ -2183,28 +2183,28 @@
         <v>1577.5</v>
       </c>
       <c r="M11">
-        <v>63.0054279</v>
+        <v>70.00603099999999</v>
       </c>
       <c r="N11">
-        <v>1514.4945721</v>
+        <v>1507.493969</v>
       </c>
       <c r="O11">
-        <v>302.89891442</v>
+        <v>301.4987938</v>
       </c>
       <c r="P11">
-        <v>1211.59565768</v>
+        <v>1205.9951752</v>
       </c>
       <c r="Q11">
-        <v>1236.59565768</v>
+        <v>1230.9951752</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1344573538029662</v>
+        <v>0.1352598643601327</v>
       </c>
       <c r="T11">
-        <v>1.062092253734638</v>
+        <v>1.071706123422211</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.03752537803175</v>
+        <v>22.53377284022858</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1257578779241194</v>
+        <v>0.1255379638875396</v>
       </c>
       <c r="C12">
-        <v>13382.17507962031</v>
+        <v>13280.08971898511</v>
       </c>
       <c r="D12">
-        <v>13448.94507962031</v>
+        <v>13486.03671898511</v>
       </c>
       <c r="E12">
-        <v>-6313.23</v>
+        <v>-6174.053</v>
       </c>
       <c r="F12">
-        <v>1391.77</v>
+        <v>1530.947</v>
       </c>
       <c r="G12">
         <v>1325</v>
@@ -2265,28 +2265,28 @@
         <v>1577.5</v>
       </c>
       <c r="M12">
-        <v>70.00603100000001</v>
+        <v>77.0066341</v>
       </c>
       <c r="N12">
-        <v>1507.493969</v>
+        <v>1500.4933659</v>
       </c>
       <c r="O12">
-        <v>301.4987938</v>
+        <v>300.09867318</v>
       </c>
       <c r="P12">
-        <v>1205.9951752</v>
+        <v>1200.39469272</v>
       </c>
       <c r="Q12">
-        <v>1230.9951752</v>
+        <v>1225.39469272</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1352598643601327</v>
+        <v>0.136080408862404</v>
       </c>
       <c r="T12">
-        <v>1.071706123422211</v>
+        <v>1.081536035125235</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.53377284022858</v>
+        <v>20.48524803657144</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1255379638875396</v>
+        <v>0.1253180498509597</v>
       </c>
       <c r="C13">
-        <v>13280.08971898511</v>
+        <v>13178.20951861607</v>
       </c>
       <c r="D13">
-        <v>13486.03671898511</v>
+        <v>13523.33351861607</v>
       </c>
       <c r="E13">
-        <v>-6174.053</v>
+        <v>-6034.876</v>
       </c>
       <c r="F13">
-        <v>1530.947</v>
+        <v>1670.124</v>
       </c>
       <c r="G13">
         <v>1325</v>
@@ -2347,28 +2347,28 @@
         <v>1577.5</v>
       </c>
       <c r="M13">
-        <v>77.0066341</v>
+        <v>84.00723719999999</v>
       </c>
       <c r="N13">
-        <v>1500.4933659</v>
+        <v>1493.4927628</v>
       </c>
       <c r="O13">
-        <v>300.09867318</v>
+        <v>298.69855256</v>
       </c>
       <c r="P13">
-        <v>1200.39469272</v>
+        <v>1194.79421024</v>
       </c>
       <c r="Q13">
-        <v>1225.39469272</v>
+        <v>1219.79421024</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.136080408862404</v>
+        <v>0.1369196021033633</v>
       </c>
       <c r="T13">
-        <v>1.081536035125235</v>
+        <v>1.091589353912419</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.48524803657144</v>
+        <v>18.77814403352382</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1253180498509597</v>
+        <v>0.1250981358143799</v>
       </c>
       <c r="C14">
-        <v>13178.20951861607</v>
+        <v>13076.53618539906</v>
       </c>
       <c r="D14">
-        <v>13523.33351861607</v>
+        <v>13560.83718539906</v>
       </c>
       <c r="E14">
-        <v>-6034.876</v>
+        <v>-5895.699</v>
       </c>
       <c r="F14">
-        <v>1670.124</v>
+        <v>1809.301</v>
       </c>
       <c r="G14">
         <v>1325</v>
@@ -2429,28 +2429,28 @@
         <v>1577.5</v>
       </c>
       <c r="M14">
-        <v>84.00723719999999</v>
+        <v>91.0078403</v>
       </c>
       <c r="N14">
-        <v>1493.4927628</v>
+        <v>1486.4921597</v>
       </c>
       <c r="O14">
-        <v>298.69855256</v>
+        <v>297.29843194</v>
       </c>
       <c r="P14">
-        <v>1194.79421024</v>
+        <v>1189.19372776</v>
       </c>
       <c r="Q14">
-        <v>1219.79421024</v>
+        <v>1214.19372776</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1369196021033633</v>
+        <v>0.1377780871429654</v>
       </c>
       <c r="T14">
-        <v>1.091589353912419</v>
+        <v>1.10187378347632</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.77814403352382</v>
+        <v>17.33367141556045</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1250981358143799</v>
+        <v>0.1248782217778001</v>
       </c>
       <c r="C15">
-        <v>13076.53618539906</v>
+        <v>12975.0714452071</v>
       </c>
       <c r="D15">
-        <v>13560.83718539906</v>
+        <v>13598.5494452071</v>
       </c>
       <c r="E15">
-        <v>-5895.699</v>
+        <v>-5756.522</v>
       </c>
       <c r="F15">
-        <v>1809.301</v>
+        <v>1948.478</v>
       </c>
       <c r="G15">
         <v>1325</v>
@@ -2511,28 +2511,28 @@
         <v>1577.5</v>
       </c>
       <c r="M15">
-        <v>91.0078403</v>
+        <v>98.0084434</v>
       </c>
       <c r="N15">
-        <v>1486.4921597</v>
+        <v>1479.4915566</v>
       </c>
       <c r="O15">
-        <v>297.29843194</v>
+        <v>295.89831132</v>
       </c>
       <c r="P15">
-        <v>1189.19372776</v>
+        <v>1183.59324528</v>
       </c>
       <c r="Q15">
-        <v>1214.19372776</v>
+        <v>1208.59324528</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1377780871429654</v>
+        <v>0.1386565369509303</v>
       </c>
       <c r="T15">
-        <v>1.10187378347632</v>
+        <v>1.112397385820776</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.33367141556045</v>
+        <v>16.0955520287347</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1248782217778001</v>
+        <v>0.1246583077412202</v>
       </c>
       <c r="C16">
-        <v>12975.0714452071</v>
+        <v>12873.8170431652</v>
       </c>
       <c r="D16">
-        <v>13598.5494452071</v>
+        <v>13636.4720431652</v>
       </c>
       <c r="E16">
-        <v>-5756.522</v>
+        <v>-5617.344999999999</v>
       </c>
       <c r="F16">
-        <v>1948.478</v>
+        <v>2087.655</v>
       </c>
       <c r="G16">
         <v>1325</v>
@@ -2593,28 +2593,28 @@
         <v>1577.5</v>
       </c>
       <c r="M16">
-        <v>98.0084434</v>
+        <v>105.0090465</v>
       </c>
       <c r="N16">
-        <v>1479.4915566</v>
+        <v>1472.4909535</v>
       </c>
       <c r="O16">
-        <v>295.89831132</v>
+        <v>294.4981907</v>
       </c>
       <c r="P16">
-        <v>1183.59324528</v>
+        <v>1177.9927628</v>
       </c>
       <c r="Q16">
-        <v>1208.59324528</v>
+        <v>1202.9927628</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1386565369509303</v>
+        <v>0.1395556561661415</v>
       </c>
       <c r="T16">
-        <v>1.112397385820776</v>
+        <v>1.123168602338044</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.0955520287347</v>
+        <v>15.02251522681905</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1246583077412202</v>
+        <v>0.1244383937046404</v>
       </c>
       <c r="C17">
-        <v>12873.8170431652</v>
+        <v>12772.77474391944</v>
       </c>
       <c r="D17">
-        <v>13636.4720431652</v>
+        <v>13674.60674391944</v>
       </c>
       <c r="E17">
-        <v>-5617.344999999999</v>
+        <v>-5478.168</v>
       </c>
       <c r="F17">
-        <v>2087.655</v>
+        <v>2226.832</v>
       </c>
       <c r="G17">
         <v>1325</v>
@@ -2675,28 +2675,28 @@
         <v>1577.5</v>
       </c>
       <c r="M17">
-        <v>105.0090465</v>
+        <v>112.0096496</v>
       </c>
       <c r="N17">
-        <v>1472.4909535</v>
+        <v>1465.4903504</v>
       </c>
       <c r="O17">
-        <v>294.4981907</v>
+        <v>293.09807008</v>
       </c>
       <c r="P17">
-        <v>1177.9927628</v>
+        <v>1172.39228032</v>
       </c>
       <c r="Q17">
-        <v>1202.9927628</v>
+        <v>1197.39228032</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1395556561661415</v>
+        <v>0.1404761829817148</v>
       </c>
       <c r="T17">
-        <v>1.123168602338044</v>
+        <v>1.134196276391436</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.02251522681905</v>
+        <v>14.08360802514286</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1244383937046404</v>
+        <v>0.1242184796680606</v>
       </c>
       <c r="C18">
-        <v>12772.77474391944</v>
+        <v>12671.94633191077</v>
       </c>
       <c r="D18">
-        <v>13674.60674391944</v>
+        <v>13712.95533191077</v>
       </c>
       <c r="E18">
-        <v>-5478.168</v>
+        <v>-5338.991</v>
       </c>
       <c r="F18">
-        <v>2226.832</v>
+        <v>2366.009</v>
       </c>
       <c r="G18">
         <v>1325</v>
@@ -2757,28 +2757,28 @@
         <v>1577.5</v>
       </c>
       <c r="M18">
-        <v>112.0096496</v>
+        <v>119.0102527</v>
       </c>
       <c r="N18">
-        <v>1465.4903504</v>
+        <v>1458.4897473</v>
       </c>
       <c r="O18">
-        <v>293.09807008</v>
+        <v>291.69794946</v>
       </c>
       <c r="P18">
-        <v>1172.39228032</v>
+        <v>1166.79179784</v>
       </c>
       <c r="Q18">
-        <v>1197.39228032</v>
+        <v>1191.79179784</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1404761829817148</v>
+        <v>0.141418891166338</v>
       </c>
       <c r="T18">
-        <v>1.134196276391436</v>
+        <v>1.145489677530453</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.08360802514286</v>
+        <v>13.2551604942521</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1242184796680606</v>
+        <v>0.1239985656314807</v>
       </c>
       <c r="C19">
-        <v>12671.94633191077</v>
+        <v>12571.33361165333</v>
       </c>
       <c r="D19">
-        <v>13712.95533191077</v>
+        <v>13751.51961165333</v>
       </c>
       <c r="E19">
-        <v>-5338.991</v>
+        <v>-5199.813999999999</v>
       </c>
       <c r="F19">
-        <v>2366.009</v>
+        <v>2505.186000000001</v>
       </c>
       <c r="G19">
         <v>1325</v>
@@ -2839,28 +2839,28 @@
         <v>1577.5</v>
       </c>
       <c r="M19">
-        <v>119.0102527</v>
+        <v>126.0108558</v>
       </c>
       <c r="N19">
-        <v>1458.4897473</v>
+        <v>1451.4891442</v>
       </c>
       <c r="O19">
-        <v>291.69794946</v>
+        <v>290.29782884</v>
       </c>
       <c r="P19">
-        <v>1166.79179784</v>
+        <v>1161.19131536</v>
       </c>
       <c r="Q19">
-        <v>1191.79179784</v>
+        <v>1186.19131536</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.141418891166338</v>
+        <v>0.1423845922335131</v>
       </c>
       <c r="T19">
-        <v>1.145489677530453</v>
+        <v>1.157058527477738</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.2551604942521</v>
+        <v>12.51876268901588</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1239985656314808</v>
+        <v>0.1237786515949009</v>
       </c>
       <c r="C20">
-        <v>12571.33361165333</v>
+        <v>12470.93840801749</v>
       </c>
       <c r="D20">
-        <v>13751.51961165333</v>
+        <v>13790.30140801749</v>
       </c>
       <c r="E20">
-        <v>-5199.814</v>
+        <v>-5060.637</v>
       </c>
       <c r="F20">
-        <v>2505.186</v>
+        <v>2644.363</v>
       </c>
       <c r="G20">
         <v>1325</v>
@@ -2921,28 +2921,28 @@
         <v>1577.5</v>
       </c>
       <c r="M20">
-        <v>126.0108558</v>
+        <v>133.0114589</v>
       </c>
       <c r="N20">
-        <v>1451.4891442</v>
+        <v>1444.4885411</v>
       </c>
       <c r="O20">
-        <v>290.29782884</v>
+        <v>288.89770822</v>
       </c>
       <c r="P20">
-        <v>1161.19131536</v>
+        <v>1155.59083288</v>
       </c>
       <c r="Q20">
-        <v>1186.19131536</v>
+        <v>1180.59083288</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1423845922335131</v>
+        <v>0.1433741377714826</v>
       </c>
       <c r="T20">
-        <v>1.157058527477738</v>
+        <v>1.168913028041006</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.51876268901588</v>
+        <v>11.85988044222557</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1237786515949009</v>
+        <v>0.1235587375583211</v>
       </c>
       <c r="C21">
-        <v>12470.93840801749</v>
+        <v>12370.76256651772</v>
       </c>
       <c r="D21">
-        <v>13790.30140801749</v>
+        <v>13829.30256651772</v>
       </c>
       <c r="E21">
-        <v>-5060.637</v>
+        <v>-4921.459999999999</v>
       </c>
       <c r="F21">
-        <v>2644.363</v>
+        <v>2783.54</v>
       </c>
       <c r="G21">
         <v>1325</v>
@@ -3003,28 +3003,28 @@
         <v>1577.5</v>
       </c>
       <c r="M21">
-        <v>133.0114589</v>
+        <v>140.012062</v>
       </c>
       <c r="N21">
-        <v>1444.4885411</v>
+        <v>1437.487938</v>
       </c>
       <c r="O21">
-        <v>288.89770822</v>
+        <v>287.4975876</v>
       </c>
       <c r="P21">
-        <v>1155.59083288</v>
+        <v>1149.9903504</v>
       </c>
       <c r="Q21">
-        <v>1180.59083288</v>
+        <v>1174.9903504</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1433741377714826</v>
+        <v>0.1443884219479013</v>
       </c>
       <c r="T21">
-        <v>1.168913028041006</v>
+        <v>1.181063891118355</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.85988044222557</v>
+        <v>11.26688642011429</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1235587375583211</v>
+        <v>0.1233388235217412</v>
       </c>
       <c r="C22">
-        <v>12370.76256651772</v>
+        <v>12270.80795360532</v>
       </c>
       <c r="D22">
-        <v>13829.30256651772</v>
+        <v>13868.52495360533</v>
       </c>
       <c r="E22">
-        <v>-4921.459999999999</v>
+        <v>-4782.282999999999</v>
       </c>
       <c r="F22">
-        <v>2783.54</v>
+        <v>2922.717000000001</v>
       </c>
       <c r="G22">
         <v>1325</v>
@@ -3085,28 +3085,28 @@
         <v>1577.5</v>
       </c>
       <c r="M22">
-        <v>140.012062</v>
+        <v>147.0126651</v>
       </c>
       <c r="N22">
-        <v>1437.487938</v>
+        <v>1430.4873349</v>
       </c>
       <c r="O22">
-        <v>287.4975876</v>
+        <v>286.09746698</v>
       </c>
       <c r="P22">
-        <v>1149.9903504</v>
+        <v>1144.38986792</v>
       </c>
       <c r="Q22">
-        <v>1174.9903504</v>
+        <v>1169.38986792</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1443884219479013</v>
+        <v>0.1454283842047357</v>
       </c>
       <c r="T22">
-        <v>1.181063891118355</v>
+        <v>1.193522370982473</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.26688642011429</v>
+        <v>10.73036801915647</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1233388235217412</v>
+        <v>0.1231189094851614</v>
       </c>
       <c r="C23">
-        <v>12270.80795360532</v>
+        <v>12171.07645696619</v>
       </c>
       <c r="D23">
-        <v>13868.52495360533</v>
+        <v>13907.97045696619</v>
       </c>
       <c r="E23">
-        <v>-4782.282999999999</v>
+        <v>-4643.106</v>
       </c>
       <c r="F23">
-        <v>2922.717</v>
+        <v>3061.894</v>
       </c>
       <c r="G23">
         <v>1325</v>
@@ -3167,28 +3167,28 @@
         <v>1577.5</v>
       </c>
       <c r="M23">
-        <v>147.0126651</v>
+        <v>154.0132682</v>
       </c>
       <c r="N23">
-        <v>1430.4873349</v>
+        <v>1423.4867318</v>
       </c>
       <c r="O23">
-        <v>286.09746698</v>
+        <v>284.69734636</v>
       </c>
       <c r="P23">
-        <v>1144.38986792</v>
+        <v>1138.78938544</v>
       </c>
       <c r="Q23">
-        <v>1169.38986792</v>
+        <v>1163.78938544</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1454283842047357</v>
+        <v>0.1464950121604633</v>
       </c>
       <c r="T23">
-        <v>1.193522370982473</v>
+        <v>1.206300299048235</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.73036801915647</v>
+        <v>10.24262401828572</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1231189094851614</v>
+        <v>0.1228989954485816</v>
       </c>
       <c r="C24">
-        <v>12171.07645696619</v>
+        <v>12071.56998582365</v>
       </c>
       <c r="D24">
-        <v>13907.97045696619</v>
+        <v>13947.64098582365</v>
       </c>
       <c r="E24">
-        <v>-4643.106</v>
+        <v>-4503.929</v>
       </c>
       <c r="F24">
-        <v>3061.894</v>
+        <v>3201.071</v>
       </c>
       <c r="G24">
         <v>1325</v>
@@ -3249,28 +3249,28 @@
         <v>1577.5</v>
       </c>
       <c r="M24">
-        <v>154.0132682</v>
+        <v>161.0138713</v>
       </c>
       <c r="N24">
-        <v>1423.4867318</v>
+        <v>1416.4861287</v>
       </c>
       <c r="O24">
-        <v>284.69734636</v>
+        <v>283.29722574</v>
       </c>
       <c r="P24">
-        <v>1138.78938544</v>
+        <v>1133.18890296</v>
       </c>
       <c r="Q24">
-        <v>1163.78938544</v>
+        <v>1158.18890296</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1464950121604633</v>
+        <v>0.1475893447384176</v>
       </c>
       <c r="T24">
-        <v>1.206300299048235</v>
+        <v>1.219410121349471</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.24262401828572</v>
+        <v>9.797292539229817</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1228989954485816</v>
+        <v>0.1226790814120017</v>
       </c>
       <c r="C25">
-        <v>12071.56998582365</v>
+        <v>11972.29047124652</v>
       </c>
       <c r="D25">
-        <v>13947.64098582365</v>
+        <v>13987.53847124652</v>
       </c>
       <c r="E25">
-        <v>-4503.929</v>
+        <v>-4364.751999999999</v>
       </c>
       <c r="F25">
-        <v>3201.071</v>
+        <v>3340.248000000001</v>
       </c>
       <c r="G25">
         <v>1325</v>
@@ -3331,28 +3331,28 @@
         <v>1577.5</v>
       </c>
       <c r="M25">
-        <v>161.0138713</v>
+        <v>168.0144744</v>
       </c>
       <c r="N25">
-        <v>1416.4861287</v>
+        <v>1409.4855256</v>
       </c>
       <c r="O25">
-        <v>283.29722574</v>
+        <v>281.89710512</v>
       </c>
       <c r="P25">
-        <v>1133.18890296</v>
+        <v>1127.58842048</v>
       </c>
       <c r="Q25">
-        <v>1158.18890296</v>
+        <v>1152.58842048</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1475893447384176</v>
+        <v>0.1487124755421076</v>
       </c>
       <c r="T25">
-        <v>1.219410121349471</v>
+        <v>1.232864938974424</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.797292539229817</v>
+        <v>9.389072016761908</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1226790814120017</v>
+        <v>0.1224591673754219</v>
       </c>
       <c r="C26">
-        <v>11972.29047124652</v>
+        <v>11873.23986646242</v>
       </c>
       <c r="D26">
-        <v>13987.53847124652</v>
+        <v>14027.66486646242</v>
       </c>
       <c r="E26">
-        <v>-4364.752</v>
+        <v>-4225.575</v>
       </c>
       <c r="F26">
-        <v>3340.248</v>
+        <v>3479.425</v>
       </c>
       <c r="G26">
         <v>1325</v>
@@ -3413,28 +3413,28 @@
         <v>1577.5</v>
       </c>
       <c r="M26">
-        <v>168.0144744</v>
+        <v>175.0150775</v>
       </c>
       <c r="N26">
-        <v>1409.4855256</v>
+        <v>1402.4849225</v>
       </c>
       <c r="O26">
-        <v>281.89710512</v>
+        <v>280.4969845</v>
       </c>
       <c r="P26">
-        <v>1127.58842048</v>
+        <v>1121.987938</v>
       </c>
       <c r="Q26">
-        <v>1152.58842048</v>
+        <v>1146.987938</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1487124755421075</v>
+        <v>0.1498655565005625</v>
       </c>
       <c r="T26">
-        <v>1.232864938974423</v>
+        <v>1.246678551736041</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.38907201676191</v>
+        <v>9.013509136091432</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1224591673754219</v>
+        <v>0.1225512533388421</v>
       </c>
       <c r="C27">
-        <v>11873.23986646242</v>
+        <v>11717.23250894291</v>
       </c>
       <c r="D27">
-        <v>14027.66486646242</v>
+        <v>14010.83450894291</v>
       </c>
       <c r="E27">
-        <v>-4225.575</v>
+        <v>-4086.398</v>
       </c>
       <c r="F27">
-        <v>3479.425</v>
+        <v>3618.602</v>
       </c>
       <c r="G27">
         <v>1325</v>
@@ -3495,45 +3495,45 @@
         <v>1577.5</v>
       </c>
       <c r="M27">
-        <v>175.0150775</v>
+        <v>187.4435836</v>
       </c>
       <c r="N27">
-        <v>1402.4849225</v>
+        <v>1390.0564164</v>
       </c>
       <c r="O27">
-        <v>280.4969845</v>
+        <v>278.01128328</v>
       </c>
       <c r="P27">
-        <v>1121.987938</v>
+        <v>1112.04513312</v>
       </c>
       <c r="Q27">
-        <v>1146.987938</v>
+        <v>1137.04513312</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1498655565005625</v>
+        <v>0.151049801809246</v>
       </c>
       <c r="T27">
-        <v>1.246678551736041</v>
+        <v>1.260865505383109</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.013509136091432</v>
+        <v>8.415865561802031</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1225512533388421</v>
+        <v>0.1223433393022622</v>
       </c>
       <c r="C28">
-        <v>11717.23250894291</v>
+        <v>11616.11302230933</v>
       </c>
       <c r="D28">
-        <v>14010.83450894291</v>
+        <v>14048.89202230933</v>
       </c>
       <c r="E28">
-        <v>-4086.398</v>
+        <v>-3947.221</v>
       </c>
       <c r="F28">
-        <v>3618.602</v>
+        <v>3757.779</v>
       </c>
       <c r="G28">
         <v>1325</v>
@@ -3577,28 +3577,28 @@
         <v>1577.5</v>
       </c>
       <c r="M28">
-        <v>187.4435836</v>
+        <v>194.6529522</v>
       </c>
       <c r="N28">
-        <v>1390.0564164</v>
+        <v>1382.8470478</v>
       </c>
       <c r="O28">
-        <v>278.01128328</v>
+        <v>276.56940956</v>
       </c>
       <c r="P28">
-        <v>1112.04513312</v>
+        <v>1106.27763824</v>
       </c>
       <c r="Q28">
-        <v>1137.04513312</v>
+        <v>1131.27763824</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.151049801809246</v>
+        <v>0.1522664921948798</v>
       </c>
       <c r="T28">
-        <v>1.260865505383109</v>
+        <v>1.27544114269174</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.415865561802031</v>
+        <v>8.104166837290844</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1223433393022622</v>
+        <v>0.1221354252656824</v>
       </c>
       <c r="C29">
-        <v>11616.11302230933</v>
+        <v>11515.20084941504</v>
       </c>
       <c r="D29">
-        <v>14048.89202230933</v>
+        <v>14087.15684941504</v>
       </c>
       <c r="E29">
-        <v>-3947.221</v>
+        <v>-3808.043999999999</v>
       </c>
       <c r="F29">
-        <v>3757.779</v>
+        <v>3896.956000000001</v>
       </c>
       <c r="G29">
         <v>1325</v>
@@ -3659,28 +3659,28 @@
         <v>1577.5</v>
       </c>
       <c r="M29">
-        <v>194.6529522</v>
+        <v>201.8623208</v>
       </c>
       <c r="N29">
-        <v>1382.8470478</v>
+        <v>1375.6376792</v>
       </c>
       <c r="O29">
-        <v>276.56940956</v>
+        <v>275.12753584</v>
       </c>
       <c r="P29">
-        <v>1106.27763824</v>
+        <v>1100.51014336</v>
       </c>
       <c r="Q29">
-        <v>1131.27763824</v>
+        <v>1125.51014336</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1522664921948798</v>
+        <v>0.15351697953567</v>
       </c>
       <c r="T29">
-        <v>1.27544114269174</v>
+        <v>1.290421658814499</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.104166837290844</v>
+        <v>7.8147323073876</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1221354252656824</v>
+        <v>0.1219275112291026</v>
       </c>
       <c r="C30">
-        <v>11515.20084941504</v>
+        <v>11414.4976888616</v>
       </c>
       <c r="D30">
-        <v>14087.15684941504</v>
+        <v>14125.6306888616</v>
       </c>
       <c r="E30">
-        <v>-3808.043999999999</v>
+        <v>-3668.866999999999</v>
       </c>
       <c r="F30">
-        <v>3896.956000000001</v>
+        <v>4036.133000000001</v>
       </c>
       <c r="G30">
         <v>1325</v>
@@ -3741,28 +3741,28 @@
         <v>1577.5</v>
       </c>
       <c r="M30">
-        <v>201.8623208</v>
+        <v>209.0716894</v>
       </c>
       <c r="N30">
-        <v>1375.6376792</v>
+        <v>1368.4283106</v>
       </c>
       <c r="O30">
-        <v>275.12753584</v>
+        <v>273.68566212</v>
       </c>
       <c r="P30">
-        <v>1100.51014336</v>
+        <v>1094.74264848</v>
       </c>
       <c r="Q30">
-        <v>1125.51014336</v>
+        <v>1119.74264848</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.15351697953567</v>
+        <v>0.1548026918719754</v>
       </c>
       <c r="T30">
-        <v>1.290421658814499</v>
+        <v>1.305824161306914</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.8147323073876</v>
+        <v>7.545258779546648</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1219275112291026</v>
+        <v>0.1217195971925227</v>
       </c>
       <c r="C31">
-        <v>11414.4976888616</v>
+        <v>11314.0052578578</v>
       </c>
       <c r="D31">
-        <v>14125.6306888616</v>
+        <v>14164.3152578578</v>
       </c>
       <c r="E31">
-        <v>-3668.867</v>
+        <v>-3529.69</v>
       </c>
       <c r="F31">
-        <v>4036.133</v>
+        <v>4175.31</v>
       </c>
       <c r="G31">
         <v>1325</v>
@@ -3823,28 +3823,28 @@
         <v>1577.5</v>
       </c>
       <c r="M31">
-        <v>209.0716894</v>
+        <v>216.281058</v>
       </c>
       <c r="N31">
-        <v>1368.4283106</v>
+        <v>1361.218942</v>
       </c>
       <c r="O31">
-        <v>273.68566212</v>
+        <v>272.2437884</v>
       </c>
       <c r="P31">
-        <v>1094.74264848</v>
+        <v>1088.9751536</v>
       </c>
       <c r="Q31">
-        <v>1119.74264848</v>
+        <v>1113.9751536</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1548026918719754</v>
+        <v>0.156125138846461</v>
       </c>
       <c r="T31">
-        <v>1.305824161306914</v>
+        <v>1.321666735299112</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.545258779546649</v>
+        <v>7.293750153561759</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1217195971925227</v>
+        <v>0.1215116831559429</v>
       </c>
       <c r="C32">
-        <v>11314.0052578578</v>
+        <v>11213.72529247509</v>
       </c>
       <c r="D32">
-        <v>14164.3152578578</v>
+        <v>14203.21229247509</v>
       </c>
       <c r="E32">
-        <v>-3529.69</v>
+        <v>-3390.513</v>
       </c>
       <c r="F32">
-        <v>4175.31</v>
+        <v>4314.487</v>
       </c>
       <c r="G32">
         <v>1325</v>
@@ -3905,28 +3905,28 @@
         <v>1577.5</v>
       </c>
       <c r="M32">
-        <v>216.281058</v>
+        <v>223.4904266</v>
       </c>
       <c r="N32">
-        <v>1361.218942</v>
+        <v>1354.0095734</v>
       </c>
       <c r="O32">
-        <v>272.2437884</v>
+        <v>270.80191468</v>
       </c>
       <c r="P32">
-        <v>1088.9751536</v>
+        <v>1083.20765872</v>
       </c>
       <c r="Q32">
-        <v>1113.9751536</v>
+        <v>1108.20765872</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.156125138846461</v>
+        <v>0.1574859176173085</v>
       </c>
       <c r="T32">
-        <v>1.321666735299112</v>
+        <v>1.337968514334562</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.293750153561759</v>
+        <v>7.058467890543638</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1215116831559429</v>
+        <v>0.1213037691193631</v>
       </c>
       <c r="C33">
-        <v>11213.72529247509</v>
+        <v>11113.65954790739</v>
       </c>
       <c r="D33">
-        <v>14203.21229247509</v>
+        <v>14242.32354790739</v>
       </c>
       <c r="E33">
-        <v>-3390.513</v>
+        <v>-3251.335999999999</v>
       </c>
       <c r="F33">
-        <v>4314.487</v>
+        <v>4453.664000000001</v>
       </c>
       <c r="G33">
         <v>1325</v>
@@ -3987,28 +3987,28 @@
         <v>1577.5</v>
       </c>
       <c r="M33">
-        <v>223.4904266</v>
+        <v>230.6997952</v>
       </c>
       <c r="N33">
-        <v>1354.0095734</v>
+        <v>1346.8002048</v>
       </c>
       <c r="O33">
-        <v>270.80191468</v>
+        <v>269.36004096</v>
       </c>
       <c r="P33">
-        <v>1083.20765872</v>
+        <v>1077.44016384</v>
       </c>
       <c r="Q33">
-        <v>1108.20765872</v>
+        <v>1102.44016384</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1574859176173085</v>
+        <v>0.158886719293181</v>
       </c>
       <c r="T33">
-        <v>1.337968514334562</v>
+        <v>1.35474975745929</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.058467890543638</v>
+        <v>6.837890768964149</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1213037691193631</v>
+        <v>0.1215446550827832</v>
       </c>
       <c r="C34">
-        <v>11113.65954790739</v>
+        <v>10929.18858194465</v>
       </c>
       <c r="D34">
-        <v>14242.32354790739</v>
+        <v>14197.02958194465</v>
       </c>
       <c r="E34">
-        <v>-3251.335999999999</v>
+        <v>-3112.159</v>
       </c>
       <c r="F34">
-        <v>4453.664000000001</v>
+        <v>4592.841</v>
       </c>
       <c r="G34">
         <v>1325</v>
@@ -4069,45 +4069,45 @@
         <v>1577.5</v>
       </c>
       <c r="M34">
-        <v>230.6997952</v>
+        <v>245.7169935</v>
       </c>
       <c r="N34">
-        <v>1346.8002048</v>
+        <v>1331.7830065</v>
       </c>
       <c r="O34">
-        <v>269.36004096</v>
+        <v>266.3566013</v>
       </c>
       <c r="P34">
-        <v>1077.44016384</v>
+        <v>1065.4264052</v>
       </c>
       <c r="Q34">
-        <v>1102.44016384</v>
+        <v>1090.4264052</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.158886719293181</v>
+        <v>0.1603293359444526</v>
       </c>
       <c r="T34">
-        <v>1.35474975745929</v>
+        <v>1.372031933214607</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.2</v>
       </c>
       <c r="W34">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>6.837890768964149</v>
+        <v>6.419987390900581</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1215446550827832</v>
+        <v>0.1213503410462033</v>
       </c>
       <c r="C35">
-        <v>10929.18858194465</v>
+        <v>10826.526071321</v>
       </c>
       <c r="D35">
-        <v>14197.02958194465</v>
+        <v>14233.544071321</v>
       </c>
       <c r="E35">
-        <v>-3112.159</v>
+        <v>-2972.981999999999</v>
       </c>
       <c r="F35">
-        <v>4592.841</v>
+        <v>4732.018000000001</v>
       </c>
       <c r="G35">
         <v>1325</v>
@@ -4151,28 +4151,28 @@
         <v>1577.5</v>
       </c>
       <c r="M35">
-        <v>245.7169935</v>
+        <v>253.162963</v>
       </c>
       <c r="N35">
-        <v>1331.7830065</v>
+        <v>1324.337037</v>
       </c>
       <c r="O35">
-        <v>266.3566013</v>
+        <v>264.8674074</v>
       </c>
       <c r="P35">
-        <v>1065.4264052</v>
+        <v>1059.4696296</v>
       </c>
       <c r="Q35">
-        <v>1090.4264052</v>
+        <v>1084.4696296</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1603293359444526</v>
+        <v>0.1618156682518233</v>
       </c>
       <c r="T35">
-        <v>1.372031933214607</v>
+        <v>1.389837811265539</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.419987390900581</v>
+        <v>6.231164232344681</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1213503410462033</v>
+        <v>0.1211560270096235</v>
       </c>
       <c r="C36">
-        <v>10826.526071321</v>
+        <v>10724.05187417686</v>
       </c>
       <c r="D36">
-        <v>14233.544071321</v>
+        <v>14270.24687417686</v>
       </c>
       <c r="E36">
-        <v>-2972.981999999999</v>
+        <v>-2833.804999999999</v>
       </c>
       <c r="F36">
-        <v>4732.018000000001</v>
+        <v>4871.195000000001</v>
       </c>
       <c r="G36">
         <v>1325</v>
@@ -4233,28 +4233,28 @@
         <v>1577.5</v>
       </c>
       <c r="M36">
-        <v>253.162963</v>
+        <v>260.6089325</v>
       </c>
       <c r="N36">
-        <v>1324.337037</v>
+        <v>1316.8910675</v>
       </c>
       <c r="O36">
-        <v>264.8674074</v>
+        <v>263.3782135</v>
       </c>
       <c r="P36">
-        <v>1059.4696296</v>
+        <v>1053.512854</v>
       </c>
       <c r="Q36">
-        <v>1084.4696296</v>
+        <v>1078.512854</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1618156682518233</v>
+        <v>0.1633477338609593</v>
       </c>
       <c r="T36">
-        <v>1.389837811265539</v>
+        <v>1.40819156248727</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.231164232344681</v>
+        <v>6.053130968563404</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1211560270096235</v>
+        <v>0.1209617129730437</v>
       </c>
       <c r="C37">
-        <v>10724.05187417686</v>
+        <v>10621.76745104118</v>
       </c>
       <c r="D37">
-        <v>14270.24687417686</v>
+        <v>14307.13945104118</v>
       </c>
       <c r="E37">
-        <v>-2833.804999999999</v>
+        <v>-2694.627999999999</v>
       </c>
       <c r="F37">
-        <v>4871.195000000001</v>
+        <v>5010.372000000001</v>
       </c>
       <c r="G37">
         <v>1325</v>
@@ -4315,28 +4315,28 @@
         <v>1577.5</v>
       </c>
       <c r="M37">
-        <v>260.6089325</v>
+        <v>268.0549020000001</v>
       </c>
       <c r="N37">
-        <v>1316.8910675</v>
+        <v>1309.445098</v>
       </c>
       <c r="O37">
-        <v>263.3782135</v>
+        <v>261.8890196</v>
       </c>
       <c r="P37">
-        <v>1053.512854</v>
+        <v>1047.5560784</v>
       </c>
       <c r="Q37">
-        <v>1078.512854</v>
+        <v>1072.5560784</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1633477338609593</v>
+        <v>0.1649276765203808</v>
       </c>
       <c r="T37">
-        <v>1.40819156248727</v>
+        <v>1.427118868434679</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.053130968563404</v>
+        <v>5.884988441658864</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1209617129730437</v>
+        <v>0.1207673989364639</v>
       </c>
       <c r="C38">
-        <v>10621.76745104119</v>
+        <v>10519.67427758555</v>
       </c>
       <c r="D38">
-        <v>14307.13945104118</v>
+        <v>14344.22327758555</v>
       </c>
       <c r="E38">
-        <v>-2694.628</v>
+        <v>-2555.451</v>
       </c>
       <c r="F38">
-        <v>5010.372</v>
+        <v>5149.549</v>
       </c>
       <c r="G38">
         <v>1325</v>
@@ -4397,28 +4397,28 @@
         <v>1577.5</v>
       </c>
       <c r="M38">
-        <v>268.054902</v>
+        <v>275.5008715</v>
       </c>
       <c r="N38">
-        <v>1309.445098</v>
+        <v>1301.9991285</v>
       </c>
       <c r="O38">
-        <v>261.8890196</v>
+        <v>260.3998257</v>
       </c>
       <c r="P38">
-        <v>1047.5560784</v>
+        <v>1041.5993028</v>
       </c>
       <c r="Q38">
-        <v>1072.5560784</v>
+        <v>1066.5993028</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1649276765203808</v>
+        <v>0.1665577760896252</v>
       </c>
       <c r="T38">
-        <v>1.427118868434679</v>
+        <v>1.446647041237562</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.884988441658865</v>
+        <v>5.72593469999241</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1207673989364639</v>
+        <v>0.120816284899884</v>
       </c>
       <c r="C39">
-        <v>10519.67427758555</v>
+        <v>10371.14955828202</v>
       </c>
       <c r="D39">
-        <v>14344.22327758555</v>
+        <v>14334.87555828202</v>
       </c>
       <c r="E39">
-        <v>-2555.451</v>
+        <v>-2416.273999999999</v>
       </c>
       <c r="F39">
-        <v>5149.549</v>
+        <v>5288.726000000001</v>
       </c>
       <c r="G39">
         <v>1325</v>
@@ -4479,45 +4479,45 @@
         <v>1577.5</v>
       </c>
       <c r="M39">
-        <v>275.5008715</v>
+        <v>287.1778218000001</v>
       </c>
       <c r="N39">
-        <v>1301.9991285</v>
+        <v>1290.3221782</v>
       </c>
       <c r="O39">
-        <v>260.3998257</v>
+        <v>258.06443564</v>
       </c>
       <c r="P39">
-        <v>1041.5993028</v>
+        <v>1032.25774256</v>
       </c>
       <c r="Q39">
-        <v>1066.5993028</v>
+        <v>1057.25774256</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1665577760896252</v>
+        <v>0.168240459515942</v>
       </c>
       <c r="T39">
-        <v>1.446647041237562</v>
+        <v>1.466805155098602</v>
       </c>
       <c r="U39">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>5.72593469999241</v>
+        <v>5.493112212191031</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.120816284899884</v>
+        <v>0.1206283708633042</v>
       </c>
       <c r="C40">
-        <v>10371.14955828202</v>
+        <v>10267.9712617009</v>
       </c>
       <c r="D40">
-        <v>14334.87555828202</v>
+        <v>14370.8742617009</v>
       </c>
       <c r="E40">
-        <v>-2416.273999999999</v>
+        <v>-2277.097</v>
       </c>
       <c r="F40">
-        <v>5288.726000000001</v>
+        <v>5427.903</v>
       </c>
       <c r="G40">
         <v>1325</v>
@@ -4561,28 +4561,28 @@
         <v>1577.5</v>
       </c>
       <c r="M40">
-        <v>287.1778218000001</v>
+        <v>294.7351329</v>
       </c>
       <c r="N40">
-        <v>1290.3221782</v>
+        <v>1282.7648671</v>
       </c>
       <c r="O40">
-        <v>258.06443564</v>
+        <v>256.55297342</v>
       </c>
       <c r="P40">
-        <v>1032.25774256</v>
+        <v>1026.21189368</v>
       </c>
       <c r="Q40">
-        <v>1057.25774256</v>
+        <v>1051.21189368</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.168240459515942</v>
+        <v>0.1699783128906626</v>
       </c>
       <c r="T40">
-        <v>1.466805155098602</v>
+        <v>1.487624190725578</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.493112212191031</v>
+        <v>5.352263181109211</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1206283708633042</v>
+        <v>0.1204404568267244</v>
       </c>
       <c r="C41">
-        <v>10267.9712617009</v>
+        <v>10164.97422504124</v>
       </c>
       <c r="D41">
-        <v>14370.8742617009</v>
+        <v>14407.05422504124</v>
       </c>
       <c r="E41">
-        <v>-2277.097</v>
+        <v>-2137.919999999999</v>
       </c>
       <c r="F41">
-        <v>5427.903</v>
+        <v>5567.080000000001</v>
       </c>
       <c r="G41">
         <v>1325</v>
@@ -4643,28 +4643,28 @@
         <v>1577.5</v>
       </c>
       <c r="M41">
-        <v>294.7351329</v>
+        <v>302.292444</v>
       </c>
       <c r="N41">
-        <v>1282.7648671</v>
+        <v>1275.207556</v>
       </c>
       <c r="O41">
-        <v>256.55297342</v>
+        <v>255.0415112</v>
       </c>
       <c r="P41">
-        <v>1026.21189368</v>
+        <v>1020.1660448</v>
       </c>
       <c r="Q41">
-        <v>1051.21189368</v>
+        <v>1045.1660448</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1699783128906626</v>
+        <v>0.1717740947112073</v>
       </c>
       <c r="T41">
-        <v>1.487624190725578</v>
+        <v>1.509137194206787</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.352263181109211</v>
+        <v>5.21845660158148</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1204404568267244</v>
+        <v>0.1202525427901445</v>
       </c>
       <c r="C42">
-        <v>10164.97422504124</v>
+        <v>10062.15982077263</v>
       </c>
       <c r="D42">
-        <v>14407.05422504124</v>
+        <v>14443.41682077263</v>
       </c>
       <c r="E42">
-        <v>-2137.919999999999</v>
+        <v>-1998.742999999999</v>
       </c>
       <c r="F42">
-        <v>5567.080000000001</v>
+        <v>5706.257000000001</v>
       </c>
       <c r="G42">
         <v>1325</v>
@@ -4725,28 +4725,28 @@
         <v>1577.5</v>
       </c>
       <c r="M42">
-        <v>302.292444</v>
+        <v>309.8497551</v>
       </c>
       <c r="N42">
-        <v>1275.207556</v>
+        <v>1267.6502449</v>
       </c>
       <c r="O42">
-        <v>255.0415112</v>
+        <v>253.53004898</v>
       </c>
       <c r="P42">
-        <v>1020.1660448</v>
+        <v>1014.12019592</v>
       </c>
       <c r="Q42">
-        <v>1045.1660448</v>
+        <v>1039.12019592</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1717740947112073</v>
+        <v>0.1736307504917704</v>
       </c>
       <c r="T42">
-        <v>1.509137194206787</v>
+        <v>1.531379452043291</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.21845660158148</v>
+        <v>5.091177172274614</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1202525427901445</v>
+        <v>0.1200646287535647</v>
       </c>
       <c r="C43">
-        <v>10062.15982077263</v>
+        <v>9959.529435255852</v>
       </c>
       <c r="D43">
-        <v>14443.41682077263</v>
+        <v>14479.96343525585</v>
       </c>
       <c r="E43">
-        <v>-1998.742999999999</v>
+        <v>-1859.565999999999</v>
       </c>
       <c r="F43">
-        <v>5706.257000000001</v>
+        <v>5845.434000000001</v>
       </c>
       <c r="G43">
         <v>1325</v>
@@ -4807,28 +4807,28 @@
         <v>1577.5</v>
       </c>
       <c r="M43">
-        <v>309.8497551</v>
+        <v>317.4070662000001</v>
       </c>
       <c r="N43">
-        <v>1267.6502449</v>
+        <v>1260.0929338</v>
       </c>
       <c r="O43">
-        <v>253.53004898</v>
+        <v>252.01858676</v>
       </c>
       <c r="P43">
-        <v>1014.12019592</v>
+        <v>1008.07434704</v>
       </c>
       <c r="Q43">
-        <v>1039.12019592</v>
+        <v>1033.07434704</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1736307504917704</v>
+        <v>0.1755514288854564</v>
       </c>
       <c r="T43">
-        <v>1.531379452043291</v>
+        <v>1.55438868428795</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.091177172274614</v>
+        <v>4.969958668172837</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1200646287535647</v>
+        <v>0.1198767147169849</v>
       </c>
       <c r="C44">
-        <v>9959.529435255852</v>
+        <v>9857.084468919107</v>
       </c>
       <c r="D44">
-        <v>14479.96343525585</v>
+        <v>14516.69546891911</v>
       </c>
       <c r="E44">
-        <v>-1859.566</v>
+        <v>-1720.389</v>
       </c>
       <c r="F44">
-        <v>5845.434</v>
+        <v>5984.611</v>
       </c>
       <c r="G44">
         <v>1325</v>
@@ -4889,28 +4889,28 @@
         <v>1577.5</v>
       </c>
       <c r="M44">
-        <v>317.4070662</v>
+        <v>324.9643773</v>
       </c>
       <c r="N44">
-        <v>1260.0929338</v>
+        <v>1252.5356227</v>
       </c>
       <c r="O44">
-        <v>252.01858676</v>
+        <v>250.50712454</v>
       </c>
       <c r="P44">
-        <v>1008.07434704</v>
+        <v>1002.02849816</v>
       </c>
       <c r="Q44">
-        <v>1033.07434704</v>
+        <v>1027.02849816</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1755514288854564</v>
+        <v>0.1775394995034822</v>
       </c>
       <c r="T44">
-        <v>1.55438868428795</v>
+        <v>1.578205258014878</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.969958668172838</v>
+        <v>4.854378234029284</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1198767147169849</v>
+        <v>0.119688800680405</v>
       </c>
       <c r="C45">
-        <v>9857.084468919107</v>
+        <v>9754.826336436852</v>
       </c>
       <c r="D45">
-        <v>14516.69546891911</v>
+        <v>14553.61433643685</v>
       </c>
       <c r="E45">
-        <v>-1720.389</v>
+        <v>-1581.212</v>
       </c>
       <c r="F45">
-        <v>5984.611</v>
+        <v>6123.788</v>
       </c>
       <c r="G45">
         <v>1325</v>
@@ -4971,28 +4971,28 @@
         <v>1577.5</v>
       </c>
       <c r="M45">
-        <v>324.9643773</v>
+        <v>332.5216884</v>
       </c>
       <c r="N45">
-        <v>1252.5356227</v>
+        <v>1244.9783116</v>
       </c>
       <c r="O45">
-        <v>250.50712454</v>
+        <v>248.99566232</v>
       </c>
       <c r="P45">
-        <v>1002.02849816</v>
+        <v>995.9826492799999</v>
       </c>
       <c r="Q45">
-        <v>1027.02849816</v>
+        <v>1020.98264928</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1775394995034822</v>
+        <v>0.1795985726435804</v>
       </c>
       <c r="T45">
-        <v>1.578205258014878</v>
+        <v>1.602872423660625</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.854378234029284</v>
+        <v>4.744051455983163</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.119688800680405</v>
+        <v>0.1195008866438252</v>
       </c>
       <c r="C46">
-        <v>9754.826336436852</v>
+        <v>9652.756466911451</v>
       </c>
       <c r="D46">
-        <v>14553.61433643685</v>
+        <v>14590.72146691145</v>
       </c>
       <c r="E46">
-        <v>-1581.212</v>
+        <v>-1442.035</v>
       </c>
       <c r="F46">
-        <v>6123.788</v>
+        <v>6262.965</v>
       </c>
       <c r="G46">
         <v>1325</v>
@@ -5053,28 +5053,28 @@
         <v>1577.5</v>
       </c>
       <c r="M46">
-        <v>332.5216884</v>
+        <v>340.0789995</v>
       </c>
       <c r="N46">
-        <v>1244.9783116</v>
+        <v>1237.4210005</v>
       </c>
       <c r="O46">
-        <v>248.99566232</v>
+        <v>247.4842001</v>
       </c>
       <c r="P46">
-        <v>995.9826492799999</v>
+        <v>989.9368004</v>
       </c>
       <c r="Q46">
-        <v>1020.98264928</v>
+        <v>1014.9368004</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1795985726435804</v>
+        <v>0.1817325211705912</v>
       </c>
       <c r="T46">
-        <v>1.602872423660625</v>
+        <v>1.628436577148035</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.744051455983163</v>
+        <v>4.638628090294649</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1195008866438252</v>
+        <v>0.1193129726072454</v>
       </c>
       <c r="C47">
-        <v>9652.756466911451</v>
+        <v>9550.876304057565</v>
       </c>
       <c r="D47">
-        <v>14590.72146691145</v>
+        <v>14628.01830405757</v>
       </c>
       <c r="E47">
-        <v>-1442.035</v>
+        <v>-1302.857999999999</v>
       </c>
       <c r="F47">
-        <v>6262.965</v>
+        <v>6402.142000000001</v>
       </c>
       <c r="G47">
         <v>1325</v>
@@ -5135,28 +5135,28 @@
         <v>1577.5</v>
       </c>
       <c r="M47">
-        <v>340.0789995</v>
+        <v>347.6363106000001</v>
       </c>
       <c r="N47">
-        <v>1237.4210005</v>
+        <v>1229.8636894</v>
       </c>
       <c r="O47">
-        <v>247.4842001</v>
+        <v>245.97273788</v>
       </c>
       <c r="P47">
-        <v>989.9368004</v>
+        <v>983.8909515199999</v>
       </c>
       <c r="Q47">
-        <v>1014.9368004</v>
+        <v>1008.89095152</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1817325211705912</v>
+        <v>0.1839455048282321</v>
       </c>
       <c r="T47">
-        <v>1.628436577148035</v>
+        <v>1.654947551134979</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.638628090294649</v>
+        <v>4.537788349201286</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1193129726072454</v>
+        <v>0.1191250585706655</v>
       </c>
       <c r="C48">
-        <v>9550.876304057565</v>
+        <v>9449.187306389402</v>
       </c>
       <c r="D48">
-        <v>14628.01830405757</v>
+        <v>14665.5063063894</v>
       </c>
       <c r="E48">
-        <v>-1302.857999999999</v>
+        <v>-1163.681</v>
       </c>
       <c r="F48">
-        <v>6402.142000000001</v>
+        <v>6541.319</v>
       </c>
       <c r="G48">
         <v>1325</v>
@@ -5217,28 +5217,28 @@
         <v>1577.5</v>
       </c>
       <c r="M48">
-        <v>347.6363106000001</v>
+        <v>355.1936217000001</v>
       </c>
       <c r="N48">
-        <v>1229.8636894</v>
+        <v>1222.3063783</v>
       </c>
       <c r="O48">
-        <v>245.97273788</v>
+        <v>244.46127566</v>
       </c>
       <c r="P48">
-        <v>983.8909515199999</v>
+        <v>977.8451026400001</v>
       </c>
       <c r="Q48">
-        <v>1008.89095152</v>
+        <v>1002.84510264</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1839455048282321</v>
+        <v>0.1862419973031425</v>
       </c>
       <c r="T48">
-        <v>1.654947551134979</v>
+        <v>1.682458939234638</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.537788349201286</v>
+        <v>4.441239660920409</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1191250585706655</v>
+        <v>0.1189371445340857</v>
       </c>
       <c r="C49">
-        <v>9449.187306389402</v>
+        <v>9347.690947410823</v>
       </c>
       <c r="D49">
-        <v>14665.5063063894</v>
+        <v>14703.18694741082</v>
       </c>
       <c r="E49">
-        <v>-1163.681</v>
+        <v>-1024.503999999999</v>
       </c>
       <c r="F49">
-        <v>6541.319</v>
+        <v>6680.496000000001</v>
       </c>
       <c r="G49">
         <v>1325</v>
@@ -5299,28 +5299,28 @@
         <v>1577.5</v>
       </c>
       <c r="M49">
-        <v>355.1936217000001</v>
+        <v>362.7509328</v>
       </c>
       <c r="N49">
-        <v>1222.3063783</v>
+        <v>1214.7490672</v>
       </c>
       <c r="O49">
-        <v>244.46127566</v>
+        <v>242.94981344</v>
       </c>
       <c r="P49">
-        <v>977.8451026400001</v>
+        <v>971.7992537599999</v>
       </c>
       <c r="Q49">
-        <v>1002.84510264</v>
+        <v>996.7992537599999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1862419973031425</v>
+        <v>0.1886268164117032</v>
       </c>
       <c r="T49">
-        <v>1.682458939234638</v>
+        <v>1.711028457645822</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.441239660920409</v>
+        <v>4.348713834651234</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1189371445340857</v>
+        <v>0.1187492304975058</v>
       </c>
       <c r="C50">
-        <v>9347.690947410825</v>
+        <v>9246.388715808422</v>
       </c>
       <c r="D50">
-        <v>14703.18694741082</v>
+        <v>14741.06171580842</v>
       </c>
       <c r="E50">
-        <v>-1024.504</v>
+        <v>-885.3269999999993</v>
       </c>
       <c r="F50">
-        <v>6680.496</v>
+        <v>6819.673000000001</v>
       </c>
       <c r="G50">
         <v>1325</v>
@@ -5381,28 +5381,28 @@
         <v>1577.5</v>
       </c>
       <c r="M50">
-        <v>362.7509328</v>
+        <v>370.3082439</v>
       </c>
       <c r="N50">
-        <v>1214.7490672</v>
+        <v>1207.1917561</v>
       </c>
       <c r="O50">
-        <v>242.94981344</v>
+        <v>241.43835122</v>
       </c>
       <c r="P50">
-        <v>971.7992537599999</v>
+        <v>965.7534048800001</v>
       </c>
       <c r="Q50">
-        <v>996.7992537599999</v>
+        <v>990.7534048800001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1886268164117032</v>
+        <v>0.1911051578382467</v>
       </c>
       <c r="T50">
-        <v>1.711028457645822</v>
+        <v>1.740718349328033</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.348713834651234</v>
+        <v>4.259964572719576</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1187492304975058</v>
+        <v>0.118961316460926</v>
       </c>
       <c r="C51">
-        <v>9246.388715808422</v>
+        <v>9064.479129421692</v>
       </c>
       <c r="D51">
-        <v>14741.06171580842</v>
+        <v>14698.32912942169</v>
       </c>
       <c r="E51">
-        <v>-885.3269999999993</v>
+        <v>-746.1499999999996</v>
       </c>
       <c r="F51">
-        <v>6819.673000000001</v>
+        <v>6958.85</v>
       </c>
       <c r="G51">
         <v>1325</v>
@@ -5463,45 +5463,45 @@
         <v>1577.5</v>
       </c>
       <c r="M51">
-        <v>370.3082439</v>
+        <v>384.824405</v>
       </c>
       <c r="N51">
-        <v>1207.1917561</v>
+        <v>1192.675595</v>
       </c>
       <c r="O51">
-        <v>241.43835122</v>
+        <v>238.535119</v>
       </c>
       <c r="P51">
-        <v>965.7534048800001</v>
+        <v>954.1404759999999</v>
       </c>
       <c r="Q51">
-        <v>990.7534048800001</v>
+        <v>979.1404759999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1911051578382467</v>
+        <v>0.193682632921852</v>
       </c>
       <c r="T51">
-        <v>1.740718349328033</v>
+        <v>1.771595836677533</v>
       </c>
       <c r="U51">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.2</v>
       </c>
       <c r="W51">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.259964572719576</v>
+        <v>4.099272238204331</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.118961316460926</v>
+        <v>0.1187814024243462</v>
       </c>
       <c r="C52">
-        <v>9064.479129421692</v>
+        <v>8961.536507452376</v>
       </c>
       <c r="D52">
-        <v>14698.32912942169</v>
+        <v>14734.56350745238</v>
       </c>
       <c r="E52">
-        <v>-746.1499999999996</v>
+        <v>-606.973</v>
       </c>
       <c r="F52">
-        <v>6958.85</v>
+        <v>7098.027</v>
       </c>
       <c r="G52">
         <v>1325</v>
@@ -5545,28 +5545,28 @@
         <v>1577.5</v>
       </c>
       <c r="M52">
-        <v>384.824405</v>
+        <v>392.5208931</v>
       </c>
       <c r="N52">
-        <v>1192.675595</v>
+        <v>1184.9791069</v>
       </c>
       <c r="O52">
-        <v>238.535119</v>
+        <v>236.99582138</v>
       </c>
       <c r="P52">
-        <v>954.1404759999999</v>
+        <v>947.98328552</v>
       </c>
       <c r="Q52">
-        <v>979.1404759999999</v>
+        <v>972.98328552</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.193682632921852</v>
+        <v>0.1963653110700943</v>
       </c>
       <c r="T52">
-        <v>1.771595836677533</v>
+        <v>1.803733629633134</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.099272238204331</v>
+        <v>4.018894351180717</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1187814024243462</v>
+        <v>0.1186014883877663</v>
       </c>
       <c r="C53">
-        <v>8961.536507452376</v>
+        <v>8858.772977239529</v>
       </c>
       <c r="D53">
-        <v>14734.56350745238</v>
+        <v>14770.97697723953</v>
       </c>
       <c r="E53">
-        <v>-606.973</v>
+        <v>-467.7959999999994</v>
       </c>
       <c r="F53">
-        <v>7098.027</v>
+        <v>7237.204000000001</v>
       </c>
       <c r="G53">
         <v>1325</v>
@@ -5627,28 +5627,28 @@
         <v>1577.5</v>
       </c>
       <c r="M53">
-        <v>392.5208931</v>
+        <v>400.2173812</v>
       </c>
       <c r="N53">
-        <v>1184.9791069</v>
+        <v>1177.2826188</v>
       </c>
       <c r="O53">
-        <v>236.99582138</v>
+        <v>235.45652376</v>
       </c>
       <c r="P53">
-        <v>947.98328552</v>
+        <v>941.8260950399999</v>
       </c>
       <c r="Q53">
-        <v>972.98328552</v>
+        <v>966.8260950399999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1963653110700943</v>
+        <v>0.1991597674745132</v>
       </c>
       <c r="T53">
-        <v>1.803733629633134</v>
+        <v>1.837210497295219</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.018894351180717</v>
+        <v>3.941607921350318</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1186014883877663</v>
+        <v>0.1184215743511865</v>
       </c>
       <c r="C54">
-        <v>8858.772977239529</v>
+        <v>8756.18986983888</v>
       </c>
       <c r="D54">
-        <v>14770.97697723953</v>
+        <v>14807.57086983888</v>
       </c>
       <c r="E54">
-        <v>-467.7959999999994</v>
+        <v>-328.6189999999997</v>
       </c>
       <c r="F54">
-        <v>7237.204000000001</v>
+        <v>7376.381</v>
       </c>
       <c r="G54">
         <v>1325</v>
@@ -5709,28 +5709,28 @@
         <v>1577.5</v>
       </c>
       <c r="M54">
-        <v>400.2173812</v>
+        <v>407.9138693</v>
       </c>
       <c r="N54">
-        <v>1177.2826188</v>
+        <v>1169.5861307</v>
       </c>
       <c r="O54">
-        <v>235.45652376</v>
+        <v>233.91722614</v>
       </c>
       <c r="P54">
-        <v>941.8260950399999</v>
+        <v>935.66890456</v>
       </c>
       <c r="Q54">
-        <v>966.8260950399999</v>
+        <v>960.66890456</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1991597674745132</v>
+        <v>0.2020731369174181</v>
       </c>
       <c r="T54">
-        <v>1.837210497295219</v>
+        <v>1.872111912517393</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.941607921350318</v>
+        <v>3.867237960570123</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1184215743511865</v>
+        <v>0.1182416603146067</v>
       </c>
       <c r="C55">
-        <v>8756.18986983888</v>
+        <v>8653.788529529236</v>
       </c>
       <c r="D55">
-        <v>14807.57086983888</v>
+        <v>14844.34652952924</v>
       </c>
       <c r="E55">
-        <v>-328.6189999999997</v>
+        <v>-189.4419999999991</v>
       </c>
       <c r="F55">
-        <v>7376.381</v>
+        <v>7515.558000000001</v>
       </c>
       <c r="G55">
         <v>1325</v>
@@ -5791,28 +5791,28 @@
         <v>1577.5</v>
       </c>
       <c r="M55">
-        <v>407.9138693</v>
+        <v>415.6103574000001</v>
       </c>
       <c r="N55">
-        <v>1169.5861307</v>
+        <v>1161.8896426</v>
       </c>
       <c r="O55">
-        <v>233.91722614</v>
+        <v>232.37792852</v>
       </c>
       <c r="P55">
-        <v>935.66890456</v>
+        <v>929.5117140799999</v>
       </c>
       <c r="Q55">
-        <v>960.66890456</v>
+        <v>954.5117140799999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2020731369174181</v>
+        <v>0.205113174596971</v>
       </c>
       <c r="T55">
-        <v>1.872111912517393</v>
+        <v>1.908530780575313</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.867237960570123</v>
+        <v>3.795622442781788</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1182416603146067</v>
+        <v>0.1180617462780268</v>
       </c>
       <c r="C56">
-        <v>8653.788529529236</v>
+        <v>8551.570313977125</v>
       </c>
       <c r="D56">
-        <v>14844.34652952924</v>
+        <v>14881.30531397713</v>
       </c>
       <c r="E56">
-        <v>-189.4419999999991</v>
+        <v>-50.26499999999942</v>
       </c>
       <c r="F56">
-        <v>7515.558000000001</v>
+        <v>7654.735000000001</v>
       </c>
       <c r="G56">
         <v>1325</v>
@@ -5873,28 +5873,28 @@
         <v>1577.5</v>
       </c>
       <c r="M56">
-        <v>415.6103574000001</v>
+        <v>423.3068455000001</v>
       </c>
       <c r="N56">
-        <v>1161.8896426</v>
+        <v>1154.1931545</v>
       </c>
       <c r="O56">
-        <v>232.37792852</v>
+        <v>230.8386309</v>
       </c>
       <c r="P56">
-        <v>929.5117140799999</v>
+        <v>923.3545236</v>
       </c>
       <c r="Q56">
-        <v>954.5117140799999</v>
+        <v>948.3545236</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.205113174596971</v>
+        <v>0.2082883250622819</v>
       </c>
       <c r="T56">
-        <v>1.908530780575313</v>
+        <v>1.946568264991363</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.795622442781788</v>
+        <v>3.726611125640301</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1180617462780268</v>
+        <v>0.117881832241447</v>
       </c>
       <c r="C57">
-        <v>8551.570313977125</v>
+        <v>8449.536594403828</v>
       </c>
       <c r="D57">
-        <v>14881.30531397713</v>
+        <v>14918.44859440383</v>
       </c>
       <c r="E57">
-        <v>-50.26499999999942</v>
+        <v>88.91200000000117</v>
       </c>
       <c r="F57">
-        <v>7654.735000000001</v>
+        <v>7793.912000000001</v>
       </c>
       <c r="G57">
         <v>1325</v>
@@ -5955,28 +5955,28 @@
         <v>1577.5</v>
       </c>
       <c r="M57">
-        <v>423.3068455000001</v>
+        <v>431.0033336000001</v>
       </c>
       <c r="N57">
-        <v>1154.1931545</v>
+        <v>1146.4966664</v>
       </c>
       <c r="O57">
-        <v>230.8386309</v>
+        <v>229.29933328</v>
       </c>
       <c r="P57">
-        <v>923.3545236</v>
+        <v>917.1973331199999</v>
       </c>
       <c r="Q57">
-        <v>948.3545236</v>
+        <v>942.1973331199999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2082883250622819</v>
+        <v>0.2116078005487432</v>
       </c>
       <c r="T57">
-        <v>1.946568264991363</v>
+        <v>1.986334725971779</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.726611125640301</v>
+        <v>3.660064498396724</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.117881832241447</v>
+        <v>0.1177019182048672</v>
       </c>
       <c r="C58">
-        <v>8449.536594403828</v>
+        <v>8347.688755754993</v>
       </c>
       <c r="D58">
-        <v>14918.44859440383</v>
+        <v>14955.77775575499</v>
       </c>
       <c r="E58">
-        <v>88.91200000000117</v>
+        <v>228.0890000000009</v>
       </c>
       <c r="F58">
-        <v>7793.912000000001</v>
+        <v>7933.089000000001</v>
       </c>
       <c r="G58">
         <v>1325</v>
@@ -6037,28 +6037,28 @@
         <v>1577.5</v>
       </c>
       <c r="M58">
-        <v>431.0033336000001</v>
+        <v>438.6998217000001</v>
       </c>
       <c r="N58">
-        <v>1146.4966664</v>
+        <v>1138.8001783</v>
       </c>
       <c r="O58">
-        <v>229.29933328</v>
+        <v>227.76003566</v>
       </c>
       <c r="P58">
-        <v>917.1973331199999</v>
+        <v>911.04014264</v>
       </c>
       <c r="Q58">
-        <v>942.1973331199999</v>
+        <v>936.04014264</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2116078005487432</v>
+        <v>0.2150816702438771</v>
       </c>
       <c r="T58">
-        <v>1.986334725971779</v>
+        <v>2.027950789788494</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.660064498396724</v>
+        <v>3.595852840530115</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1177019182048672</v>
+        <v>0.1175220041682873</v>
       </c>
       <c r="C59">
-        <v>8347.688755754993</v>
+        <v>8246.028196872778</v>
       </c>
       <c r="D59">
-        <v>14955.77775575499</v>
+        <v>14993.29419687278</v>
       </c>
       <c r="E59">
-        <v>228.0890000000009</v>
+        <v>367.2660000000014</v>
       </c>
       <c r="F59">
-        <v>7933.089000000001</v>
+        <v>8072.266000000001</v>
       </c>
       <c r="G59">
         <v>1325</v>
@@ -6119,28 +6119,28 @@
         <v>1577.5</v>
       </c>
       <c r="M59">
-        <v>438.6998217000001</v>
+        <v>446.3963098000001</v>
       </c>
       <c r="N59">
-        <v>1138.8001783</v>
+        <v>1131.1036902</v>
       </c>
       <c r="O59">
-        <v>227.76003566</v>
+        <v>226.22073804</v>
       </c>
       <c r="P59">
-        <v>911.04014264</v>
+        <v>904.8829521599998</v>
       </c>
       <c r="Q59">
-        <v>936.04014264</v>
+        <v>929.8829521599998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2150816702438771</v>
+        <v>0.218720962305446</v>
       </c>
       <c r="T59">
-        <v>2.027950789788494</v>
+        <v>2.071548570929814</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.595852840530115</v>
+        <v>3.533855377762353</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1175220041682873</v>
+        <v>0.1173420901317075</v>
       </c>
       <c r="C60">
-        <v>8246.02819687278</v>
+        <v>8144.556330670552</v>
       </c>
       <c r="D60">
-        <v>14993.29419687278</v>
+        <v>15030.99933067055</v>
       </c>
       <c r="E60">
-        <v>367.2659999999996</v>
+        <v>506.4429999999993</v>
       </c>
       <c r="F60">
-        <v>8072.266</v>
+        <v>8211.442999999999</v>
       </c>
       <c r="G60">
         <v>1325</v>
@@ -6201,28 +6201,28 @@
         <v>1577.5</v>
       </c>
       <c r="M60">
-        <v>446.3963098</v>
+        <v>454.0927979</v>
       </c>
       <c r="N60">
-        <v>1131.1036902</v>
+        <v>1123.4072021</v>
       </c>
       <c r="O60">
-        <v>226.22073804</v>
+        <v>224.68144042</v>
       </c>
       <c r="P60">
-        <v>904.8829521600001</v>
+        <v>898.72576168</v>
       </c>
       <c r="Q60">
-        <v>929.8829521600001</v>
+        <v>923.72576168</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2187209623054459</v>
+        <v>0.2225377808090426</v>
       </c>
       <c r="T60">
-        <v>2.071548570929813</v>
+        <v>2.117273073102417</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.533855377762355</v>
+        <v>3.473959523901975</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1173420901317075</v>
+        <v>0.1171621760951276</v>
       </c>
       <c r="C61">
-        <v>8144.556330670552</v>
+        <v>8043.274584310306</v>
       </c>
       <c r="D61">
-        <v>15030.99933067055</v>
+        <v>15068.89458431031</v>
       </c>
       <c r="E61">
-        <v>506.4429999999993</v>
+        <v>645.6200000000008</v>
       </c>
       <c r="F61">
-        <v>8211.442999999999</v>
+        <v>8350.620000000001</v>
       </c>
       <c r="G61">
         <v>1325</v>
@@ -6283,28 +6283,28 @@
         <v>1577.5</v>
       </c>
       <c r="M61">
-        <v>454.0927979</v>
+        <v>461.7892860000001</v>
       </c>
       <c r="N61">
-        <v>1123.4072021</v>
+        <v>1115.710714</v>
       </c>
       <c r="O61">
-        <v>224.68144042</v>
+        <v>223.1421428</v>
       </c>
       <c r="P61">
-        <v>898.72576168</v>
+        <v>892.5685711999998</v>
       </c>
       <c r="Q61">
-        <v>923.72576168</v>
+        <v>917.5685711999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2225377808090426</v>
+        <v>0.2265454402378191</v>
       </c>
       <c r="T61">
-        <v>2.117273073102417</v>
+        <v>2.165283800383651</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.473959523901975</v>
+        <v>3.416060198503609</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1171621760951276</v>
+        <v>0.1169822620585478</v>
       </c>
       <c r="C62">
-        <v>8043.274584310306</v>
+        <v>7942.184399382711</v>
       </c>
       <c r="D62">
-        <v>15068.89458431031</v>
+        <v>15106.98139938271</v>
       </c>
       <c r="E62">
-        <v>645.6200000000008</v>
+        <v>784.7970000000005</v>
       </c>
       <c r="F62">
-        <v>8350.620000000001</v>
+        <v>8489.797</v>
       </c>
       <c r="G62">
         <v>1325</v>
@@ -6365,28 +6365,28 @@
         <v>1577.5</v>
       </c>
       <c r="M62">
-        <v>461.7892860000001</v>
+        <v>469.4857741</v>
       </c>
       <c r="N62">
-        <v>1115.710714</v>
+        <v>1108.0142259</v>
       </c>
       <c r="O62">
-        <v>223.1421428</v>
+        <v>221.60284518</v>
       </c>
       <c r="P62">
-        <v>892.5685711999998</v>
+        <v>886.4113807199999</v>
       </c>
       <c r="Q62">
-        <v>917.5685711999998</v>
+        <v>911.4113807199999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2265454402378191</v>
+        <v>0.2307586206629431</v>
       </c>
       <c r="T62">
-        <v>2.165283800383651</v>
+        <v>2.21575661624341</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.416060198503609</v>
+        <v>3.360059211642894</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1169822620585478</v>
+        <v>0.116802348021968</v>
       </c>
       <c r="C63">
-        <v>7942.184399382711</v>
+        <v>7841.287232089913</v>
       </c>
       <c r="D63">
-        <v>15106.98139938271</v>
+        <v>15145.26123208991</v>
       </c>
       <c r="E63">
-        <v>784.7970000000005</v>
+        <v>923.9740000000002</v>
       </c>
       <c r="F63">
-        <v>8489.797</v>
+        <v>8628.974</v>
       </c>
       <c r="G63">
         <v>1325</v>
@@ -6447,28 +6447,28 @@
         <v>1577.5</v>
       </c>
       <c r="M63">
-        <v>469.4857741</v>
+        <v>477.1822622</v>
       </c>
       <c r="N63">
-        <v>1108.0142259</v>
+        <v>1100.3177378</v>
       </c>
       <c r="O63">
-        <v>221.60284518</v>
+        <v>220.06354756</v>
       </c>
       <c r="P63">
-        <v>886.4113807199999</v>
+        <v>880.2541902400001</v>
       </c>
       <c r="Q63">
-        <v>911.4113807199999</v>
+        <v>905.2541902400001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2307586206629431</v>
+        <v>0.2351935474262315</v>
       </c>
       <c r="T63">
-        <v>2.21575661624341</v>
+        <v>2.268885896095787</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.360059211642894</v>
+        <v>3.305864708229299</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.116802348021968</v>
+        <v>0.1166224339853882</v>
       </c>
       <c r="C64">
-        <v>7841.287232089913</v>
+        <v>7740.584553431132</v>
       </c>
       <c r="D64">
-        <v>15145.26123208991</v>
+        <v>15183.73555343113</v>
       </c>
       <c r="E64">
-        <v>923.9740000000002</v>
+        <v>1063.151</v>
       </c>
       <c r="F64">
-        <v>8628.974</v>
+        <v>8768.151</v>
       </c>
       <c r="G64">
         <v>1325</v>
@@ -6529,28 +6529,28 @@
         <v>1577.5</v>
       </c>
       <c r="M64">
-        <v>477.1822622</v>
+        <v>484.8787503</v>
       </c>
       <c r="N64">
-        <v>1100.3177378</v>
+        <v>1092.6212497</v>
       </c>
       <c r="O64">
-        <v>220.06354756</v>
+        <v>218.52424994</v>
       </c>
       <c r="P64">
-        <v>880.2541902400001</v>
+        <v>874.0969997599999</v>
       </c>
       <c r="Q64">
-        <v>905.2541902400001</v>
+        <v>899.0969997599999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2351935474262315</v>
+        <v>0.2398681999605085</v>
       </c>
       <c r="T64">
-        <v>2.268885896095787</v>
+        <v>2.324887028913159</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.305864708229299</v>
+        <v>3.253390665241532</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1166224339853882</v>
+        <v>0.1164425199488083</v>
       </c>
       <c r="C65">
-        <v>7740.584553431132</v>
+        <v>7640.077849391106</v>
       </c>
       <c r="D65">
-        <v>15183.73555343113</v>
+        <v>15222.40584939111</v>
       </c>
       <c r="E65">
-        <v>1063.151</v>
+        <v>1202.328000000001</v>
       </c>
       <c r="F65">
-        <v>8768.151</v>
+        <v>8907.328000000001</v>
       </c>
       <c r="G65">
         <v>1325</v>
@@ -6611,28 +6611,28 @@
         <v>1577.5</v>
       </c>
       <c r="M65">
-        <v>484.8787503</v>
+        <v>492.5752384000001</v>
       </c>
       <c r="N65">
-        <v>1092.6212497</v>
+        <v>1084.9247616</v>
       </c>
       <c r="O65">
-        <v>218.52424994</v>
+        <v>216.98495232</v>
       </c>
       <c r="P65">
-        <v>874.0969997599999</v>
+        <v>867.9398092799998</v>
       </c>
       <c r="Q65">
-        <v>899.0969997599999</v>
+        <v>892.9398092799998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2398681999605085</v>
+        <v>0.2448025554133564</v>
       </c>
       <c r="T65">
-        <v>2.324887028913159</v>
+        <v>2.383999335775939</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.253390665241532</v>
+        <v>3.202556436097133</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1164425199488083</v>
+        <v>0.1162626059122285</v>
       </c>
       <c r="C66">
-        <v>7640.077849391106</v>
+        <v>7539.76862113137</v>
       </c>
       <c r="D66">
-        <v>15222.40584939111</v>
+        <v>15261.27362113137</v>
       </c>
       <c r="E66">
-        <v>1202.328000000001</v>
+        <v>1341.505000000001</v>
       </c>
       <c r="F66">
-        <v>8907.328000000001</v>
+        <v>9046.505000000001</v>
       </c>
       <c r="G66">
         <v>1325</v>
@@ -6693,28 +6693,28 @@
         <v>1577.5</v>
       </c>
       <c r="M66">
-        <v>492.5752384000001</v>
+        <v>500.2717265000001</v>
       </c>
       <c r="N66">
-        <v>1084.9247616</v>
+        <v>1077.2282735</v>
       </c>
       <c r="O66">
-        <v>216.98495232</v>
+        <v>215.4456547</v>
       </c>
       <c r="P66">
-        <v>867.9398092799998</v>
+        <v>861.7826187999999</v>
       </c>
       <c r="Q66">
-        <v>892.9398092799998</v>
+        <v>886.7826187999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2448025554133564</v>
+        <v>0.2500188740349384</v>
       </c>
       <c r="T66">
-        <v>2.383999335775939</v>
+        <v>2.446489488745164</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.202556436097133</v>
+        <v>3.153286337080254</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1162626059122285</v>
+        <v>0.1160826918756486</v>
       </c>
       <c r="C67">
-        <v>7539.76862113137</v>
+        <v>7439.658385184535</v>
       </c>
       <c r="D67">
-        <v>15261.27362113137</v>
+        <v>15300.34038518453</v>
       </c>
       <c r="E67">
-        <v>1341.505000000001</v>
+        <v>1480.682000000001</v>
       </c>
       <c r="F67">
-        <v>9046.505000000001</v>
+        <v>9185.682000000001</v>
       </c>
       <c r="G67">
         <v>1325</v>
@@ -6775,28 +6775,28 @@
         <v>1577.5</v>
       </c>
       <c r="M67">
-        <v>500.2717265000001</v>
+        <v>507.9682146000001</v>
       </c>
       <c r="N67">
-        <v>1077.2282735</v>
+        <v>1069.5317854</v>
       </c>
       <c r="O67">
-        <v>215.4456547</v>
+        <v>213.90635708</v>
       </c>
       <c r="P67">
-        <v>861.7826187999999</v>
+        <v>855.62542832</v>
       </c>
       <c r="Q67">
-        <v>886.7826187999999</v>
+        <v>880.62542832</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2500188740349384</v>
+        <v>0.2555420349283783</v>
       </c>
       <c r="T67">
-        <v>2.446489488745164</v>
+        <v>2.51265553306552</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.153286337080254</v>
+        <v>3.105509271366917</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1160826918756486</v>
+        <v>0.1159027778390688</v>
       </c>
       <c r="C68">
-        <v>7439.658385184535</v>
+        <v>7339.748673651517</v>
       </c>
       <c r="D68">
-        <v>15300.34038518453</v>
+        <v>15339.60767365152</v>
       </c>
       <c r="E68">
-        <v>1480.682000000001</v>
+        <v>1619.859</v>
       </c>
       <c r="F68">
-        <v>9185.682000000001</v>
+        <v>9324.859</v>
       </c>
       <c r="G68">
         <v>1325</v>
@@ -6857,28 +6857,28 @@
         <v>1577.5</v>
       </c>
       <c r="M68">
-        <v>507.9682146000001</v>
+        <v>515.6647027</v>
       </c>
       <c r="N68">
-        <v>1069.5317854</v>
+        <v>1061.8352973</v>
       </c>
       <c r="O68">
-        <v>213.90635708</v>
+        <v>212.36705946</v>
       </c>
       <c r="P68">
-        <v>855.62542832</v>
+        <v>849.46823784</v>
       </c>
       <c r="Q68">
-        <v>880.62542832</v>
+        <v>874.46823784</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2555420349283783</v>
+        <v>0.261399932845663</v>
       </c>
       <c r="T68">
-        <v>2.51265553306552</v>
+        <v>2.58283164067802</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.105509271366917</v>
+        <v>3.05915838671965</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1159027778390688</v>
+        <v>0.1157228638024889</v>
       </c>
       <c r="C69">
-        <v>7339.748673651517</v>
+        <v>7240.041034401866</v>
       </c>
       <c r="D69">
-        <v>15339.60767365152</v>
+        <v>15379.07703440187</v>
       </c>
       <c r="E69">
-        <v>1619.859</v>
+        <v>1759.036000000002</v>
       </c>
       <c r="F69">
-        <v>9324.859</v>
+        <v>9464.036000000002</v>
       </c>
       <c r="G69">
         <v>1325</v>
@@ -6939,28 +6939,28 @@
         <v>1577.5</v>
       </c>
       <c r="M69">
-        <v>515.6647027</v>
+        <v>523.3611908000001</v>
       </c>
       <c r="N69">
-        <v>1061.8352973</v>
+        <v>1054.1388092</v>
       </c>
       <c r="O69">
-        <v>212.36705946</v>
+        <v>210.82776184</v>
       </c>
       <c r="P69">
-        <v>849.46823784</v>
+        <v>843.3110473599997</v>
       </c>
       <c r="Q69">
-        <v>874.46823784</v>
+        <v>868.3110473599997</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.261399932845663</v>
+        <v>0.267623949382778</v>
       </c>
       <c r="T69">
-        <v>2.58283164067802</v>
+        <v>2.657393755016299</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.05915838671965</v>
+        <v>3.014170763385537</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1157228638024889</v>
+        <v>0.1169229497659091</v>
       </c>
       <c r="C70">
-        <v>7240.041034401866</v>
+        <v>6841.366719680113</v>
       </c>
       <c r="D70">
-        <v>15379.07703440187</v>
+        <v>15119.57971968012</v>
       </c>
       <c r="E70">
-        <v>1759.036000000002</v>
+        <v>1898.213000000002</v>
       </c>
       <c r="F70">
-        <v>9464.036000000002</v>
+        <v>9603.213000000002</v>
       </c>
       <c r="G70">
         <v>1325</v>
@@ -7021,45 +7021,45 @@
         <v>1577.5</v>
       </c>
       <c r="M70">
-        <v>523.3611908000001</v>
+        <v>555.0657114000002</v>
       </c>
       <c r="N70">
-        <v>1054.1388092</v>
+        <v>1022.4342886</v>
       </c>
       <c r="O70">
-        <v>210.82776184</v>
+        <v>204.48685772</v>
       </c>
       <c r="P70">
-        <v>843.3110473599997</v>
+        <v>817.9474308799998</v>
       </c>
       <c r="Q70">
-        <v>868.3110473599997</v>
+        <v>842.9474308799998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.267623949382778</v>
+        <v>0.2742495153739005</v>
       </c>
       <c r="T70">
-        <v>2.657393755016299</v>
+        <v>2.736766328344146</v>
       </c>
       <c r="U70">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V70">
         <v>0.2</v>
       </c>
       <c r="W70">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>3.014170763385537</v>
+        <v>2.842005851921913</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1169229497659091</v>
+        <v>0.1167630357293293</v>
       </c>
       <c r="C71">
-        <v>6841.366719680113</v>
+        <v>6736.261444480437</v>
       </c>
       <c r="D71">
-        <v>15119.57971968012</v>
+        <v>15153.65144448044</v>
       </c>
       <c r="E71">
-        <v>1898.213000000002</v>
+        <v>2037.390000000001</v>
       </c>
       <c r="F71">
-        <v>9603.213000000002</v>
+        <v>9742.390000000001</v>
       </c>
       <c r="G71">
         <v>1325</v>
@@ -7103,28 +7103,28 @@
         <v>1577.5</v>
       </c>
       <c r="M71">
-        <v>555.0657114000002</v>
+        <v>563.1101420000001</v>
       </c>
       <c r="N71">
-        <v>1022.4342886</v>
+        <v>1014.389858</v>
       </c>
       <c r="O71">
-        <v>204.48685772</v>
+        <v>202.8779716</v>
       </c>
       <c r="P71">
-        <v>817.9474308799998</v>
+        <v>811.5118863999999</v>
       </c>
       <c r="Q71">
-        <v>842.9474308799998</v>
+        <v>836.5118863999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2742495153739005</v>
+        <v>0.281316785764431</v>
       </c>
       <c r="T71">
-        <v>2.736766328344146</v>
+        <v>2.821430406560515</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.842005851921913</v>
+        <v>2.801405768323028</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1167630357293293</v>
+        <v>0.1166031216927495</v>
       </c>
       <c r="C72">
-        <v>6736.261444480437</v>
+        <v>6631.31007625309</v>
       </c>
       <c r="D72">
-        <v>15153.65144448044</v>
+        <v>15187.87707625309</v>
       </c>
       <c r="E72">
-        <v>2037.390000000001</v>
+        <v>2176.567000000001</v>
       </c>
       <c r="F72">
-        <v>9742.390000000001</v>
+        <v>9881.567000000001</v>
       </c>
       <c r="G72">
         <v>1325</v>
@@ -7185,28 +7185,28 @@
         <v>1577.5</v>
       </c>
       <c r="M72">
-        <v>563.1101420000001</v>
+        <v>571.1545726000001</v>
       </c>
       <c r="N72">
-        <v>1014.389858</v>
+        <v>1006.3454274</v>
       </c>
       <c r="O72">
-        <v>202.8779716</v>
+        <v>201.26908548</v>
       </c>
       <c r="P72">
-        <v>811.5118863999999</v>
+        <v>805.07634192</v>
       </c>
       <c r="Q72">
-        <v>836.5118863999999</v>
+        <v>830.07634192</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.281316785764431</v>
+        <v>0.2888714541129292</v>
       </c>
       <c r="T72">
-        <v>2.821430406560515</v>
+        <v>2.911933386722842</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.801405768323028</v>
+        <v>2.761949349050874</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1166031216927495</v>
+        <v>0.1164432076561696</v>
       </c>
       <c r="C73">
-        <v>6631.31007625309</v>
+        <v>6526.513660189239</v>
       </c>
       <c r="D73">
-        <v>15187.87707625309</v>
+        <v>15222.25766018924</v>
       </c>
       <c r="E73">
-        <v>2176.567000000001</v>
+        <v>2315.744000000001</v>
       </c>
       <c r="F73">
-        <v>9881.567000000001</v>
+        <v>10020.744</v>
       </c>
       <c r="G73">
         <v>1325</v>
@@ -7267,28 +7267,28 @@
         <v>1577.5</v>
       </c>
       <c r="M73">
-        <v>571.1545726000001</v>
+        <v>579.1990032000001</v>
       </c>
       <c r="N73">
-        <v>1006.3454274</v>
+        <v>998.3009967999999</v>
       </c>
       <c r="O73">
-        <v>201.26908548</v>
+        <v>199.66019936</v>
       </c>
       <c r="P73">
-        <v>805.07634192</v>
+        <v>798.6407974399999</v>
       </c>
       <c r="Q73">
-        <v>830.07634192</v>
+        <v>823.6407974399999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2888714541129291</v>
+        <v>0.2969657416291772</v>
       </c>
       <c r="T73">
-        <v>2.911933386722841</v>
+        <v>3.00890086546819</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.761949349050874</v>
+        <v>2.723588941425167</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1164432076561696</v>
+        <v>0.1162832936195898</v>
       </c>
       <c r="C74">
-        <v>6526.513660189239</v>
+        <v>6421.873250965453</v>
       </c>
       <c r="D74">
-        <v>15222.25766018924</v>
+        <v>15256.79425096545</v>
       </c>
       <c r="E74">
-        <v>2315.744000000001</v>
+        <v>2454.921</v>
       </c>
       <c r="F74">
-        <v>10020.744</v>
+        <v>10159.921</v>
       </c>
       <c r="G74">
         <v>1325</v>
@@ -7349,28 +7349,28 @@
         <v>1577.5</v>
       </c>
       <c r="M74">
-        <v>579.1990032000001</v>
+        <v>587.2434338</v>
       </c>
       <c r="N74">
-        <v>998.3009967999999</v>
+        <v>990.2565662</v>
       </c>
       <c r="O74">
-        <v>199.66019936</v>
+        <v>198.05131324</v>
       </c>
       <c r="P74">
-        <v>798.6407974399999</v>
+        <v>792.2052529599999</v>
       </c>
       <c r="Q74">
-        <v>823.6407974399999</v>
+        <v>817.2052529599999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2969657416291772</v>
+        <v>0.3056596059984806</v>
       </c>
       <c r="T74">
-        <v>3.00890086546819</v>
+        <v>3.113051120416898</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.723588941425167</v>
+        <v>2.686279503871398</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1162832936195898</v>
+        <v>0.11612337958301</v>
       </c>
       <c r="C75">
-        <v>6421.873250965453</v>
+        <v>6317.389912851539</v>
       </c>
       <c r="D75">
-        <v>15256.79425096545</v>
+        <v>15291.48791285154</v>
       </c>
       <c r="E75">
-        <v>2454.921</v>
+        <v>2594.098</v>
       </c>
       <c r="F75">
-        <v>10159.921</v>
+        <v>10299.098</v>
       </c>
       <c r="G75">
         <v>1325</v>
@@ -7431,28 +7431,28 @@
         <v>1577.5</v>
       </c>
       <c r="M75">
-        <v>587.2434338</v>
+        <v>595.2878644</v>
       </c>
       <c r="N75">
-        <v>990.2565662</v>
+        <v>982.2121356</v>
       </c>
       <c r="O75">
-        <v>198.05131324</v>
+        <v>196.44242712</v>
       </c>
       <c r="P75">
-        <v>792.2052529599999</v>
+        <v>785.76970848</v>
       </c>
       <c r="Q75">
-        <v>817.2052529599999</v>
+        <v>810.76970848</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3056596059984806</v>
+        <v>0.3150222291654229</v>
       </c>
       <c r="T75">
-        <v>3.113051120416898</v>
+        <v>3.225212933438585</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.686279503871398</v>
+        <v>2.649978429494757</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.11612337958301</v>
+        <v>0.1159634655464301</v>
       </c>
       <c r="C76">
-        <v>6317.389912851539</v>
+        <v>6213.0647198199</v>
       </c>
       <c r="D76">
-        <v>15291.48791285154</v>
+        <v>15326.3397198199</v>
       </c>
       <c r="E76">
-        <v>2594.098</v>
+        <v>2733.275000000001</v>
       </c>
       <c r="F76">
-        <v>10299.098</v>
+        <v>10438.275</v>
       </c>
       <c r="G76">
         <v>1325</v>
@@ -7513,28 +7513,28 @@
         <v>1577.5</v>
       </c>
       <c r="M76">
-        <v>595.2878644</v>
+        <v>603.3322950000002</v>
       </c>
       <c r="N76">
-        <v>982.2121356</v>
+        <v>974.1677049999998</v>
       </c>
       <c r="O76">
-        <v>196.44242712</v>
+        <v>194.833541</v>
       </c>
       <c r="P76">
-        <v>785.76970848</v>
+        <v>779.3341639999999</v>
       </c>
       <c r="Q76">
-        <v>810.76970848</v>
+        <v>804.3341639999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3150222291654229</v>
+        <v>0.3251338621857205</v>
       </c>
       <c r="T76">
-        <v>3.225212933438585</v>
+        <v>3.346347691502007</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.649978429494757</v>
+        <v>2.61464538376816</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1159634655464301</v>
+        <v>0.1158035515098503</v>
       </c>
       <c r="C77">
-        <v>6213.0647198199</v>
+        <v>6108.898755656355</v>
       </c>
       <c r="D77">
-        <v>15326.3397198199</v>
+        <v>15361.35075565636</v>
       </c>
       <c r="E77">
-        <v>2733.275000000001</v>
+        <v>2872.452000000001</v>
       </c>
       <c r="F77">
-        <v>10438.275</v>
+        <v>10577.452</v>
       </c>
       <c r="G77">
         <v>1325</v>
@@ -7595,28 +7595,28 @@
         <v>1577.5</v>
       </c>
       <c r="M77">
-        <v>603.3322950000002</v>
+        <v>611.3767256000001</v>
       </c>
       <c r="N77">
-        <v>974.1677049999998</v>
+        <v>966.1232743999999</v>
       </c>
       <c r="O77">
-        <v>194.833541</v>
+        <v>193.22465488</v>
       </c>
       <c r="P77">
-        <v>779.3341639999999</v>
+        <v>772.8986195199999</v>
       </c>
       <c r="Q77">
-        <v>804.3341639999999</v>
+        <v>797.8986195199999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3251338621857205</v>
+        <v>0.3360881312910429</v>
       </c>
       <c r="T77">
-        <v>3.346347691502007</v>
+        <v>3.477577012737379</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.61464538376816</v>
+        <v>2.580242155034369</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1158035515098503</v>
+        <v>0.1156436374732705</v>
       </c>
       <c r="C78">
-        <v>6108.898755656355</v>
+        <v>6004.893114072445</v>
       </c>
       <c r="D78">
-        <v>15361.35075565636</v>
+        <v>15396.52211407244</v>
       </c>
       <c r="E78">
-        <v>2872.452000000001</v>
+        <v>3011.629000000001</v>
       </c>
       <c r="F78">
-        <v>10577.452</v>
+        <v>10716.629</v>
       </c>
       <c r="G78">
         <v>1325</v>
@@ -7677,28 +7677,28 @@
         <v>1577.5</v>
       </c>
       <c r="M78">
-        <v>611.3767256000001</v>
+        <v>619.4211562</v>
       </c>
       <c r="N78">
-        <v>966.1232743999999</v>
+        <v>958.0788438</v>
       </c>
       <c r="O78">
-        <v>193.22465488</v>
+        <v>191.61576876</v>
       </c>
       <c r="P78">
-        <v>772.8986195199999</v>
+        <v>766.4630750399999</v>
       </c>
       <c r="Q78">
-        <v>797.8986195199999</v>
+        <v>791.4630750399999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3360881312910429</v>
+        <v>0.3479949455359585</v>
       </c>
       <c r="T78">
-        <v>3.477577012737379</v>
+        <v>3.620217579297567</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.580242155034369</v>
+        <v>2.546732516657299</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1156436374732705</v>
+        <v>0.1154837234366906</v>
       </c>
       <c r="C79">
-        <v>6004.893114072445</v>
+        <v>5901.048898819361</v>
       </c>
       <c r="D79">
-        <v>15396.52211407244</v>
+        <v>15431.85489881936</v>
       </c>
       <c r="E79">
-        <v>3011.629000000001</v>
+        <v>3150.806</v>
       </c>
       <c r="F79">
-        <v>10716.629</v>
+        <v>10855.806</v>
       </c>
       <c r="G79">
         <v>1325</v>
@@ -7759,28 +7759,28 @@
         <v>1577.5</v>
       </c>
       <c r="M79">
-        <v>619.4211562</v>
+        <v>627.4655868000001</v>
       </c>
       <c r="N79">
-        <v>958.0788438</v>
+        <v>950.0344131999999</v>
       </c>
       <c r="O79">
-        <v>191.61576876</v>
+        <v>190.00688264</v>
       </c>
       <c r="P79">
-        <v>766.4630750399999</v>
+        <v>760.0275305599999</v>
       </c>
       <c r="Q79">
-        <v>791.4630750399999</v>
+        <v>785.0275305599999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3479949455359585</v>
+        <v>0.3609841974395028</v>
       </c>
       <c r="T79">
-        <v>3.620217579297567</v>
+        <v>3.775825470090499</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.546732516657299</v>
+        <v>2.514082099777077</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1154837234366906</v>
+        <v>0.1175358094001108</v>
       </c>
       <c r="C80">
-        <v>5901.048898819361</v>
+        <v>5320.425805268278</v>
       </c>
       <c r="D80">
-        <v>15431.85489881936</v>
+        <v>14990.40880526828</v>
       </c>
       <c r="E80">
-        <v>3150.806</v>
+        <v>3289.983</v>
       </c>
       <c r="F80">
-        <v>10855.806</v>
+        <v>10994.983</v>
       </c>
       <c r="G80">
         <v>1325</v>
@@ -7841,45 +7841,45 @@
         <v>1577.5</v>
       </c>
       <c r="M80">
-        <v>627.4655868000001</v>
+        <v>673.9924579</v>
       </c>
       <c r="N80">
-        <v>950.0344131999999</v>
+        <v>903.5075421</v>
       </c>
       <c r="O80">
-        <v>190.00688264</v>
+        <v>180.70150842</v>
       </c>
       <c r="P80">
-        <v>760.0275305599999</v>
+        <v>722.80603368</v>
       </c>
       <c r="Q80">
-        <v>785.0275305599999</v>
+        <v>747.80603368</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3609841974395028</v>
+        <v>0.3752105209529085</v>
       </c>
       <c r="T80">
-        <v>3.775825470090499</v>
+        <v>3.946253160006568</v>
       </c>
       <c r="U80">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V80">
         <v>0.2</v>
       </c>
       <c r="W80">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.514082099777077</v>
+        <v>2.34053064171536</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1175358094001108</v>
+        <v>0.1174038953635309</v>
       </c>
       <c r="C81">
-        <v>5320.425805268278</v>
+        <v>5208.865254421575</v>
       </c>
       <c r="D81">
-        <v>14990.40880526828</v>
+        <v>15018.02525442158</v>
       </c>
       <c r="E81">
-        <v>3289.983</v>
+        <v>3429.160000000002</v>
       </c>
       <c r="F81">
-        <v>10994.983</v>
+        <v>11134.16</v>
       </c>
       <c r="G81">
         <v>1325</v>
@@ -7923,28 +7923,28 @@
         <v>1577.5</v>
       </c>
       <c r="M81">
-        <v>673.9924579</v>
+        <v>682.5240080000001</v>
       </c>
       <c r="N81">
-        <v>903.5075421</v>
+        <v>894.9759919999999</v>
       </c>
       <c r="O81">
-        <v>180.70150842</v>
+        <v>178.9951984</v>
       </c>
       <c r="P81">
-        <v>722.80603368</v>
+        <v>715.9807936</v>
       </c>
       <c r="Q81">
-        <v>747.80603368</v>
+        <v>740.9807936</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3752105209529085</v>
+        <v>0.3908594768176548</v>
       </c>
       <c r="T81">
-        <v>3.946253160006568</v>
+        <v>4.133723618914244</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.34053064171536</v>
+        <v>2.311274008693918</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1174038953635309</v>
+        <v>0.1172719813269511</v>
       </c>
       <c r="C82">
-        <v>5208.865254421575</v>
+        <v>5097.406645544748</v>
       </c>
       <c r="D82">
-        <v>15018.02525442158</v>
+        <v>15045.74364554475</v>
       </c>
       <c r="E82">
-        <v>3429.160000000002</v>
+        <v>3568.337000000001</v>
       </c>
       <c r="F82">
-        <v>11134.16</v>
+        <v>11273.337</v>
       </c>
       <c r="G82">
         <v>1325</v>
@@ -8005,28 +8005,28 @@
         <v>1577.5</v>
       </c>
       <c r="M82">
-        <v>682.5240080000001</v>
+        <v>691.0555581000001</v>
       </c>
       <c r="N82">
-        <v>894.9759919999999</v>
+        <v>886.4444418999999</v>
       </c>
       <c r="O82">
-        <v>178.9951984</v>
+        <v>177.28888838</v>
       </c>
       <c r="P82">
-        <v>715.9807936</v>
+        <v>709.1555535199999</v>
       </c>
       <c r="Q82">
-        <v>740.9807936</v>
+        <v>734.1555535199999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3908594768176548</v>
+        <v>0.4081556911944796</v>
       </c>
       <c r="T82">
-        <v>4.133723618914244</v>
+        <v>4.340927810338517</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.311274008693918</v>
+        <v>2.282739761673005</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1172719813269511</v>
+        <v>0.1171400672903713</v>
       </c>
       <c r="C83">
-        <v>5097.406645544748</v>
+        <v>4986.050544136711</v>
       </c>
       <c r="D83">
-        <v>15045.74364554475</v>
+        <v>15073.56454413671</v>
       </c>
       <c r="E83">
-        <v>3568.337000000001</v>
+        <v>3707.514000000001</v>
       </c>
       <c r="F83">
-        <v>11273.337</v>
+        <v>11412.514</v>
       </c>
       <c r="G83">
         <v>1325</v>
@@ -8087,28 +8087,28 @@
         <v>1577.5</v>
       </c>
       <c r="M83">
-        <v>691.0555581000001</v>
+        <v>699.5871082000001</v>
       </c>
       <c r="N83">
-        <v>886.4444418999999</v>
+        <v>877.9128917999999</v>
       </c>
       <c r="O83">
-        <v>177.28888838</v>
+        <v>175.58257836</v>
       </c>
       <c r="P83">
-        <v>709.1555535199999</v>
+        <v>702.3303134399999</v>
       </c>
       <c r="Q83">
-        <v>734.1555535199999</v>
+        <v>727.3303134399999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4081556911944796</v>
+        <v>0.4273737071687294</v>
       </c>
       <c r="T83">
-        <v>4.340927810338517</v>
+        <v>4.57115468969882</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.282739761673005</v>
+        <v>2.254901471896505</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1171400672903713</v>
+        <v>0.1188673532537914</v>
       </c>
       <c r="C84">
-        <v>4986.050544136711</v>
+        <v>4490.539897215618</v>
       </c>
       <c r="D84">
-        <v>15073.56454413671</v>
+        <v>14717.23089721562</v>
       </c>
       <c r="E84">
-        <v>3707.514000000001</v>
+        <v>3846.691000000001</v>
       </c>
       <c r="F84">
-        <v>11412.514</v>
+        <v>11551.691</v>
       </c>
       <c r="G84">
         <v>1325</v>
@@ -8169,45 +8169,45 @@
         <v>1577.5</v>
       </c>
       <c r="M84">
-        <v>699.5871082000001</v>
+        <v>740.4633931000001</v>
       </c>
       <c r="N84">
-        <v>877.9128917999999</v>
+        <v>837.0366068999999</v>
       </c>
       <c r="O84">
-        <v>175.58257836</v>
+        <v>167.40732138</v>
       </c>
       <c r="P84">
-        <v>702.3303134399999</v>
+        <v>669.6292855199999</v>
       </c>
       <c r="Q84">
-        <v>727.3303134399999</v>
+        <v>694.6292855199999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4273737071687294</v>
+        <v>0.4488526661987733</v>
       </c>
       <c r="T84">
-        <v>4.57115468969882</v>
+        <v>4.828467084277984</v>
       </c>
       <c r="U84">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V84">
         <v>0.2</v>
       </c>
       <c r="W84">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.254901471896505</v>
+        <v>2.130422671397285</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1188673532537914</v>
+        <v>0.1187578392172116</v>
       </c>
       <c r="C85">
-        <v>4490.539897215618</v>
+        <v>4373.454332215944</v>
       </c>
       <c r="D85">
-        <v>14717.23089721562</v>
+        <v>14739.32233221595</v>
       </c>
       <c r="E85">
-        <v>3846.691000000001</v>
+        <v>3985.868000000002</v>
       </c>
       <c r="F85">
-        <v>11551.691</v>
+        <v>11690.868</v>
       </c>
       <c r="G85">
         <v>1325</v>
@@ -8251,28 +8251,28 @@
         <v>1577.5</v>
       </c>
       <c r="M85">
-        <v>740.4633931000001</v>
+        <v>749.3846388000002</v>
       </c>
       <c r="N85">
-        <v>837.0366068999999</v>
+        <v>828.1153611999998</v>
       </c>
       <c r="O85">
-        <v>167.40732138</v>
+        <v>165.62307224</v>
       </c>
       <c r="P85">
-        <v>669.6292855199999</v>
+        <v>662.4922889599999</v>
       </c>
       <c r="Q85">
-        <v>694.6292855199999</v>
+        <v>687.4922889599999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4488526661987733</v>
+        <v>0.4730164951075727</v>
       </c>
       <c r="T85">
-        <v>4.828467084277984</v>
+        <v>5.117943528179541</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.130422671397285</v>
+        <v>2.105060496737793</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1187578392172116</v>
+        <v>0.1186483251806318</v>
       </c>
       <c r="C86">
-        <v>4373.454332215952</v>
+        <v>4256.435188021829</v>
       </c>
       <c r="D86">
-        <v>14739.32233221595</v>
+        <v>14761.48018802183</v>
       </c>
       <c r="E86">
-        <v>3985.868</v>
+        <v>4125.045</v>
       </c>
       <c r="F86">
-        <v>11690.868</v>
+        <v>11830.045</v>
       </c>
       <c r="G86">
         <v>1325</v>
@@ -8333,28 +8333,28 @@
         <v>1577.5</v>
       </c>
       <c r="M86">
-        <v>749.3846388000001</v>
+        <v>758.3058845</v>
       </c>
       <c r="N86">
-        <v>828.1153611999999</v>
+        <v>819.1941155</v>
       </c>
       <c r="O86">
-        <v>165.62307224</v>
+        <v>163.8388231</v>
       </c>
       <c r="P86">
-        <v>662.49228896</v>
+        <v>655.3552923999999</v>
       </c>
       <c r="Q86">
-        <v>687.49228896</v>
+        <v>680.3552923999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4730164951075724</v>
+        <v>0.5004021678708783</v>
       </c>
       <c r="T86">
-        <v>5.117943528179538</v>
+        <v>5.44601683126797</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.105060496737793</v>
+        <v>2.080295079129113</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1186483251806318</v>
+        <v>0.1185388111440519</v>
       </c>
       <c r="C87">
-        <v>4256.435188021829</v>
+        <v>4139.482764638595</v>
       </c>
       <c r="D87">
-        <v>14761.48018802183</v>
+        <v>14783.70476463859</v>
       </c>
       <c r="E87">
-        <v>4125.045</v>
+        <v>4264.222</v>
       </c>
       <c r="F87">
-        <v>11830.045</v>
+        <v>11969.222</v>
       </c>
       <c r="G87">
         <v>1325</v>
@@ -8415,28 +8415,28 @@
         <v>1577.5</v>
       </c>
       <c r="M87">
-        <v>758.3058845</v>
+        <v>767.2271302</v>
       </c>
       <c r="N87">
-        <v>819.1941155</v>
+        <v>810.2728698</v>
       </c>
       <c r="O87">
-        <v>163.8388231</v>
+        <v>162.05457396</v>
       </c>
       <c r="P87">
-        <v>655.3552923999999</v>
+        <v>648.21829584</v>
       </c>
       <c r="Q87">
-        <v>680.3552923999999</v>
+        <v>673.21829584</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5004021678708783</v>
+        <v>0.5317000796003708</v>
       </c>
       <c r="T87">
-        <v>5.44601683126797</v>
+        <v>5.820957749083322</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.080295079129113</v>
+        <v>2.056105601464822</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1185388111440519</v>
+        <v>0.1184292971074721</v>
       </c>
       <c r="C88">
-        <v>4139.482764638595</v>
+        <v>4022.597363881037</v>
       </c>
       <c r="D88">
-        <v>14783.70476463859</v>
+        <v>14805.99636388104</v>
       </c>
       <c r="E88">
-        <v>4264.222</v>
+        <v>4403.399000000001</v>
       </c>
       <c r="F88">
-        <v>11969.222</v>
+        <v>12108.399</v>
       </c>
       <c r="G88">
         <v>1325</v>
@@ -8497,28 +8497,28 @@
         <v>1577.5</v>
       </c>
       <c r="M88">
-        <v>767.2271302</v>
+        <v>776.1483759000001</v>
       </c>
       <c r="N88">
-        <v>810.2728698</v>
+        <v>801.3516240999999</v>
       </c>
       <c r="O88">
-        <v>162.05457396</v>
+        <v>160.27032482</v>
       </c>
       <c r="P88">
-        <v>648.21829584</v>
+        <v>641.0812992799999</v>
       </c>
       <c r="Q88">
-        <v>673.21829584</v>
+        <v>666.0812992799999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5317000796003708</v>
+        <v>0.5678130546728621</v>
       </c>
       <c r="T88">
-        <v>5.820957749083322</v>
+        <v>6.25358188502411</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.056105601464822</v>
+        <v>2.032472203746835</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1184292971074721</v>
+        <v>0.1183197830708922</v>
       </c>
       <c r="C89">
-        <v>4022.597363881037</v>
+        <v>3905.779289387063</v>
       </c>
       <c r="D89">
-        <v>14805.99636388104</v>
+        <v>14828.35528938706</v>
       </c>
       <c r="E89">
-        <v>4403.399000000001</v>
+        <v>4542.576000000001</v>
       </c>
       <c r="F89">
-        <v>12108.399</v>
+        <v>12247.576</v>
       </c>
       <c r="G89">
         <v>1325</v>
@@ -8579,28 +8579,28 @@
         <v>1577.5</v>
       </c>
       <c r="M89">
-        <v>776.1483759000001</v>
+        <v>785.0696216000001</v>
       </c>
       <c r="N89">
-        <v>801.3516240999999</v>
+        <v>792.4303783999999</v>
       </c>
       <c r="O89">
-        <v>160.27032482</v>
+        <v>158.48607568</v>
       </c>
       <c r="P89">
-        <v>641.0812992799999</v>
+        <v>633.9443027199999</v>
       </c>
       <c r="Q89">
-        <v>666.0812992799999</v>
+        <v>658.9443027199999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5678130546728621</v>
+        <v>0.6099448589241021</v>
       </c>
       <c r="T89">
-        <v>6.25358188502411</v>
+        <v>6.758310043621699</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.032472203746835</v>
+        <v>2.009375928704257</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1183197830708922</v>
+        <v>0.1237638690343124</v>
       </c>
       <c r="C90">
-        <v>3905.779289387063</v>
+        <v>2731.163157242005</v>
       </c>
       <c r="D90">
-        <v>14828.35528938706</v>
+        <v>13792.91615724201</v>
       </c>
       <c r="E90">
-        <v>4542.576000000001</v>
+        <v>4681.753000000001</v>
       </c>
       <c r="F90">
-        <v>12247.576</v>
+        <v>12386.753</v>
       </c>
       <c r="G90">
         <v>1325</v>
@@ -8661,45 +8661,45 @@
         <v>1577.5</v>
       </c>
       <c r="M90">
-        <v>785.0696216000001</v>
+        <v>890.6075407000001</v>
       </c>
       <c r="N90">
-        <v>792.4303783999999</v>
+        <v>686.8924592999999</v>
       </c>
       <c r="O90">
-        <v>158.48607568</v>
+        <v>137.37849186</v>
       </c>
       <c r="P90">
-        <v>633.9443027199999</v>
+        <v>549.51396744</v>
       </c>
       <c r="Q90">
-        <v>658.9443027199999</v>
+        <v>574.51396744</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6099448589241021</v>
+        <v>0.659736991221022</v>
       </c>
       <c r="T90">
-        <v>6.758310043621699</v>
+        <v>7.35480695832794</v>
       </c>
       <c r="U90">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V90">
         <v>0.2</v>
       </c>
       <c r="W90">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.009375928704257</v>
+        <v>1.771262792991979</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1237638690343124</v>
+        <v>0.1237167549977326</v>
       </c>
       <c r="C91">
-        <v>2731.163157242005</v>
+        <v>2600.326339740541</v>
       </c>
       <c r="D91">
-        <v>13792.91615724201</v>
+        <v>13801.25633974054</v>
       </c>
       <c r="E91">
-        <v>4681.753000000001</v>
+        <v>4820.93</v>
       </c>
       <c r="F91">
-        <v>12386.753</v>
+        <v>12525.93</v>
       </c>
       <c r="G91">
         <v>1325</v>
@@ -8743,28 +8743,28 @@
         <v>1577.5</v>
       </c>
       <c r="M91">
-        <v>890.6075407000001</v>
+        <v>900.6143670000001</v>
       </c>
       <c r="N91">
-        <v>686.8924592999999</v>
+        <v>676.8856329999999</v>
       </c>
       <c r="O91">
-        <v>137.37849186</v>
+        <v>135.3771266</v>
       </c>
       <c r="P91">
-        <v>549.51396744</v>
+        <v>541.5085063999999</v>
       </c>
       <c r="Q91">
-        <v>574.51396744</v>
+        <v>566.5085063999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.659736991221022</v>
+        <v>0.719487549977326</v>
       </c>
       <c r="T91">
-        <v>7.35480695832794</v>
+        <v>8.070603255975429</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.771262792991979</v>
+        <v>1.751582095292068</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1237167549977326</v>
+        <v>0.1265088409611527</v>
       </c>
       <c r="C92">
-        <v>2600.326339740541</v>
+        <v>1983.701099314188</v>
       </c>
       <c r="D92">
-        <v>13801.25633974054</v>
+        <v>13323.80809931419</v>
       </c>
       <c r="E92">
-        <v>4820.93</v>
+        <v>4960.107000000002</v>
       </c>
       <c r="F92">
-        <v>12525.93</v>
+        <v>12665.107</v>
       </c>
       <c r="G92">
         <v>1325</v>
@@ -8825,45 +8825,45 @@
         <v>1577.5</v>
       </c>
       <c r="M92">
-        <v>900.6143670000001</v>
+        <v>960.0151106000002</v>
       </c>
       <c r="N92">
-        <v>676.8856329999999</v>
+        <v>617.4848893999998</v>
       </c>
       <c r="O92">
-        <v>135.3771266</v>
+        <v>123.49697788</v>
       </c>
       <c r="P92">
-        <v>541.5085063999999</v>
+        <v>493.9879115199998</v>
       </c>
       <c r="Q92">
-        <v>566.5085063999999</v>
+        <v>518.9879115199999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.719487549977326</v>
+        <v>0.7925160106794751</v>
       </c>
       <c r="T92">
-        <v>8.070603255975429</v>
+        <v>8.945465397544581</v>
       </c>
       <c r="U92">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V92">
         <v>0.2</v>
       </c>
       <c r="W92">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y92">
-        <v>1.751582095292068</v>
+        <v>1.643203302304354</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1265088409611527</v>
+        <v>0.1264929269245729</v>
       </c>
       <c r="C93">
-        <v>1983.701099314188</v>
+        <v>1847.151784014148</v>
       </c>
       <c r="D93">
-        <v>13323.80809931419</v>
+        <v>13326.43578401415</v>
       </c>
       <c r="E93">
-        <v>4960.107000000002</v>
+        <v>5099.284000000001</v>
       </c>
       <c r="F93">
-        <v>12665.107</v>
+        <v>12804.284</v>
       </c>
       <c r="G93">
         <v>1325</v>
@@ -8907,28 +8907,28 @@
         <v>1577.5</v>
       </c>
       <c r="M93">
-        <v>960.0151106000002</v>
+        <v>970.5647272000002</v>
       </c>
       <c r="N93">
-        <v>617.4848893999998</v>
+        <v>606.9352727999998</v>
       </c>
       <c r="O93">
-        <v>123.49697788</v>
+        <v>121.38705456</v>
       </c>
       <c r="P93">
-        <v>493.9879115199998</v>
+        <v>485.5482182399998</v>
       </c>
       <c r="Q93">
-        <v>518.9879115199999</v>
+        <v>510.5482182399998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7925160106794751</v>
+        <v>0.8838015865571618</v>
       </c>
       <c r="T93">
-        <v>8.945465397544581</v>
+        <v>10.03904307450602</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.643203302304354</v>
+        <v>1.625342396844524</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1264929269245729</v>
+        <v>0.1264770128879931</v>
       </c>
       <c r="C94">
-        <v>1847.151784014148</v>
+        <v>1710.60350536803</v>
       </c>
       <c r="D94">
-        <v>13326.43578401415</v>
+        <v>13329.06450536803</v>
       </c>
       <c r="E94">
-        <v>5099.284000000001</v>
+        <v>5238.461000000001</v>
       </c>
       <c r="F94">
-        <v>12804.284</v>
+        <v>12943.461</v>
       </c>
       <c r="G94">
         <v>1325</v>
@@ -8989,28 +8989,28 @@
         <v>1577.5</v>
       </c>
       <c r="M94">
-        <v>970.5647272000002</v>
+        <v>981.1143438000001</v>
       </c>
       <c r="N94">
-        <v>606.9352727999998</v>
+        <v>596.3856561999999</v>
       </c>
       <c r="O94">
-        <v>121.38705456</v>
+        <v>119.27713124</v>
       </c>
       <c r="P94">
-        <v>485.5482182399998</v>
+        <v>477.1085249599999</v>
       </c>
       <c r="Q94">
-        <v>510.5482182399998</v>
+        <v>502.1085249599999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8838015865571618</v>
+        <v>1.001168755542759</v>
       </c>
       <c r="T94">
-        <v>10.03904307450602</v>
+        <v>11.44507151631359</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.625342396844524</v>
+        <v>1.607865596878454</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1264770128879931</v>
+        <v>0.1264610988514132</v>
       </c>
       <c r="C95">
-        <v>1710.60350536803</v>
+        <v>1574.056263989396</v>
       </c>
       <c r="D95">
-        <v>13329.06450536803</v>
+        <v>13331.6942639894</v>
       </c>
       <c r="E95">
-        <v>5238.461000000001</v>
+        <v>5377.638000000001</v>
       </c>
       <c r="F95">
-        <v>12943.461</v>
+        <v>13082.638</v>
       </c>
       <c r="G95">
         <v>1325</v>
@@ -9071,28 +9071,28 @@
         <v>1577.5</v>
       </c>
       <c r="M95">
-        <v>981.1143438000001</v>
+        <v>991.6639604000002</v>
       </c>
       <c r="N95">
-        <v>596.3856561999999</v>
+        <v>585.8360395999998</v>
       </c>
       <c r="O95">
-        <v>119.27713124</v>
+        <v>117.16720792</v>
       </c>
       <c r="P95">
-        <v>477.1085249599999</v>
+        <v>468.6688316799999</v>
       </c>
       <c r="Q95">
-        <v>502.1085249599999</v>
+        <v>493.6688316799999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.001168755542759</v>
+        <v>1.157658314190222</v>
       </c>
       <c r="T95">
-        <v>11.44507151631359</v>
+        <v>13.31977610539035</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.607865596878454</v>
+        <v>1.590760643720173</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1264610988514132</v>
+        <v>0.1264451848148334</v>
       </c>
       <c r="C96">
-        <v>1574.056263989396</v>
+        <v>1437.510060492308</v>
       </c>
       <c r="D96">
-        <v>13331.6942639894</v>
+        <v>13334.32506049231</v>
       </c>
       <c r="E96">
-        <v>5377.638000000001</v>
+        <v>5516.815000000002</v>
       </c>
       <c r="F96">
-        <v>13082.638</v>
+        <v>13221.815</v>
       </c>
       <c r="G96">
         <v>1325</v>
@@ -9153,28 +9153,28 @@
         <v>1577.5</v>
       </c>
       <c r="M96">
-        <v>991.6639604000002</v>
+        <v>1002.213577</v>
       </c>
       <c r="N96">
-        <v>585.8360395999998</v>
+        <v>575.2864229999998</v>
       </c>
       <c r="O96">
-        <v>117.16720792</v>
+        <v>115.0572846</v>
       </c>
       <c r="P96">
-        <v>468.6688316799999</v>
+        <v>460.2291383999998</v>
       </c>
       <c r="Q96">
-        <v>493.6688316799999</v>
+        <v>485.2291383999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.157658314190222</v>
+        <v>1.37674369629667</v>
       </c>
       <c r="T96">
-        <v>13.31977610539035</v>
+        <v>15.94436253009782</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.590760643720173</v>
+        <v>1.574015794838908</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1264451848148334</v>
+        <v>0.1264292707782536</v>
       </c>
       <c r="C97">
-        <v>1437.510060492308</v>
+        <v>1300.964895491339</v>
       </c>
       <c r="D97">
-        <v>13334.32506049231</v>
+        <v>13336.95689549134</v>
       </c>
       <c r="E97">
-        <v>5516.815000000002</v>
+        <v>5655.992000000002</v>
       </c>
       <c r="F97">
-        <v>13221.815</v>
+        <v>13360.992</v>
       </c>
       <c r="G97">
         <v>1325</v>
@@ -9235,28 +9235,28 @@
         <v>1577.5</v>
       </c>
       <c r="M97">
-        <v>1002.213577</v>
+        <v>1012.7631936</v>
       </c>
       <c r="N97">
-        <v>575.2864229999998</v>
+        <v>564.7368063999998</v>
       </c>
       <c r="O97">
-        <v>115.0572846</v>
+        <v>112.94736128</v>
       </c>
       <c r="P97">
-        <v>460.2291383999998</v>
+        <v>451.7894451199998</v>
       </c>
       <c r="Q97">
-        <v>485.2291383999998</v>
+        <v>476.7894451199998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.37674369629667</v>
+        <v>1.705371769456342</v>
       </c>
       <c r="T97">
-        <v>15.94436253009782</v>
+        <v>19.88124216715902</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.574015794838908</v>
+        <v>1.557619796976002</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1264292707782536</v>
+        <v>0.1264133567416738</v>
       </c>
       <c r="C98">
-        <v>1300.964895491341</v>
+        <v>1164.420769601502</v>
       </c>
       <c r="D98">
-        <v>13336.95689549134</v>
+        <v>13339.5897696015</v>
       </c>
       <c r="E98">
-        <v>5655.992</v>
+        <v>5795.169</v>
       </c>
       <c r="F98">
-        <v>13360.992</v>
+        <v>13500.169</v>
       </c>
       <c r="G98">
         <v>1325</v>
@@ -9317,28 +9317,28 @@
         <v>1577.5</v>
       </c>
       <c r="M98">
-        <v>1012.7631936</v>
+        <v>1023.3128102</v>
       </c>
       <c r="N98">
-        <v>564.7368063999999</v>
+        <v>554.1871897999999</v>
       </c>
       <c r="O98">
-        <v>112.94736128</v>
+        <v>110.83743796</v>
       </c>
       <c r="P98">
-        <v>451.7894451199999</v>
+        <v>443.34975184</v>
       </c>
       <c r="Q98">
-        <v>476.7894451199999</v>
+        <v>468.34975184</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.705371769456338</v>
+        <v>2.253085224722456</v>
       </c>
       <c r="T98">
-        <v>19.88124216715896</v>
+        <v>26.4427082289276</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.557619796976002</v>
+        <v>1.541561860924703</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1264133567416738</v>
+        <v>0.1263974427050939</v>
       </c>
       <c r="C99">
-        <v>1164.420769601502</v>
+        <v>1027.877683438328</v>
       </c>
       <c r="D99">
-        <v>13339.5897696015</v>
+        <v>13342.22368343833</v>
       </c>
       <c r="E99">
-        <v>5795.169</v>
+        <v>5934.346000000001</v>
       </c>
       <c r="F99">
-        <v>13500.169</v>
+        <v>13639.346</v>
       </c>
       <c r="G99">
         <v>1325</v>
@@ -9399,28 +9399,28 @@
         <v>1577.5</v>
       </c>
       <c r="M99">
-        <v>1023.3128102</v>
+        <v>1033.8624268</v>
       </c>
       <c r="N99">
-        <v>554.1871897999999</v>
+        <v>543.6375731999999</v>
       </c>
       <c r="O99">
-        <v>110.83743796</v>
+        <v>108.72751464</v>
       </c>
       <c r="P99">
-        <v>443.34975184</v>
+        <v>434.9100585599999</v>
       </c>
       <c r="Q99">
-        <v>468.34975184</v>
+        <v>459.9100585599999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.253085224722456</v>
+        <v>3.348512135254692</v>
       </c>
       <c r="T99">
-        <v>26.4427082289276</v>
+        <v>39.56564035246486</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.541561860924703</v>
+        <v>1.525831637854043</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1263974427050939</v>
+        <v>0.126381528668514</v>
       </c>
       <c r="C100">
-        <v>1027.877683438328</v>
+        <v>891.3356376178181</v>
       </c>
       <c r="D100">
-        <v>13342.22368343833</v>
+        <v>13344.85863761782</v>
       </c>
       <c r="E100">
-        <v>5934.346000000001</v>
+        <v>6073.523000000001</v>
       </c>
       <c r="F100">
-        <v>13639.346</v>
+        <v>13778.523</v>
       </c>
       <c r="G100">
         <v>1325</v>
@@ -9481,28 +9481,28 @@
         <v>1577.5</v>
       </c>
       <c r="M100">
-        <v>1033.8624268</v>
+        <v>1044.4120434</v>
       </c>
       <c r="N100">
-        <v>543.6375731999999</v>
+        <v>533.0879565999999</v>
       </c>
       <c r="O100">
-        <v>108.72751464</v>
+        <v>106.61759132</v>
       </c>
       <c r="P100">
-        <v>434.9100585599999</v>
+        <v>426.4703652799999</v>
       </c>
       <c r="Q100">
-        <v>459.9100585599999</v>
+        <v>451.4703652799999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.348512135254692</v>
+        <v>6.6347928668514</v>
       </c>
       <c r="T100">
-        <v>39.56564035246486</v>
+        <v>78.93443672307666</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.525831637854043</v>
+        <v>1.510419197067639</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.126381528668514</v>
-      </c>
-      <c r="C101">
-        <v>891.3356376178181</v>
-      </c>
-      <c r="D101">
-        <v>13344.85863761782</v>
-      </c>
-      <c r="E101">
-        <v>6073.523000000001</v>
-      </c>
-      <c r="F101">
-        <v>13778.523</v>
-      </c>
-      <c r="G101">
-        <v>1325</v>
-      </c>
-      <c r="H101">
-        <v>6212.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1602.5</v>
-      </c>
-      <c r="K101">
-        <v>25</v>
-      </c>
-      <c r="L101">
-        <v>1577.5</v>
-      </c>
-      <c r="M101">
-        <v>1044.4120434</v>
-      </c>
-      <c r="N101">
-        <v>533.0879565999999</v>
-      </c>
-      <c r="O101">
-        <v>106.61759132</v>
-      </c>
-      <c r="P101">
-        <v>426.4703652799999</v>
-      </c>
-      <c r="Q101">
-        <v>451.4703652799999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.6347928668514</v>
-      </c>
-      <c r="T101">
-        <v>78.93443672307666</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.06064000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.510419197067639</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
